--- a/data/bist_screener_2026-08-06.xlsx
+++ b/data/bist_screener_2026-08-06.xlsx
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4465</v>
+        <v>4475</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
@@ -657,23 +657,23 @@
       <c r="E2" s="5" t="n">
         <v>2247.5</v>
       </c>
-      <c r="F2" s="5" t="n">
-        <v>1497.5</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>4750</v>
+      <c r="F2" s="3" t="n">
+        <v>1495</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>4752.5</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.4311</v>
+        <v>0.4343</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>4490</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>91.84</v>
+        <v>92.36</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>2937.5</v>
@@ -694,37 +694,37 @@
         </is>
       </c>
       <c r="P2" s="5" t="n">
-        <v>647.5</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>4480</v>
+        <v>650</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>4482.5</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>3900</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="T2" s="5" t="n">
         <v>247.5</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.0555</v>
+        <v>0.0554</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.0673</v>
+        <v>0.0672</v>
       </c>
       <c r="W2" s="5" t="n">
         <v>62.6</v>
       </c>
       <c r="X2" s="5" t="n">
-        <v>74.52</v>
+        <v>74.53</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>3845</v>
       </c>
       <c r="Z2" s="5" t="n">
-        <v>-1.21</v>
+        <v>-0.73</v>
       </c>
       <c r="AA2" s="5" t="n">
         <v>42.62</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>103</v>
+        <v>103.2</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>0.5</v>
@@ -759,13 +759,13 @@
         <v>0.06</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>-0.1997</v>
+        <v>-0.1981</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>148</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>51.36</v>
+        <v>51.47</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>112</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -789,22 +789,22 @@
         <v>6.2</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="R3" s="7" t="n">
         <v>126.6</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>-14</v>
+        <v>-13.8</v>
       </c>
       <c r="T3" s="7" t="n">
         <v>10.4</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>0.1008</v>
+        <v>0.1006</v>
       </c>
       <c r="V3" s="8" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="W3" s="7" t="n">
         <v>31.82</v>
@@ -816,7 +816,7 @@
         <v>139</v>
       </c>
       <c r="Z3" s="7" t="n">
-        <v>-81.81999999999999</v>
+        <v>-81.45</v>
       </c>
       <c r="AA3" s="7" t="n">
         <v>27.78</v>
@@ -829,8 +829,8 @@
           <t>ODINE</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>2647.5</v>
+      <c r="B4" s="3" t="n">
+        <v>2605</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>0.9286</v>
@@ -842,25 +842,25 @@
         <v>1927.5</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>175</v>
+        <v>187.5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2905</v>
+        <v>2900</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0547</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>3047.5</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>64.09</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>2442.5</v>
+        <v>62.16</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>2440</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -878,37 +878,37 @@
         </is>
       </c>
       <c r="P4" s="5" t="n">
-        <v>235</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>2827.5</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>2852.5</v>
+        <v>232.5</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>2815</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2850</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>307.5</v>
+        <v>265</v>
       </c>
       <c r="T4" s="5" t="n">
         <v>202.5</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.0762</v>
+        <v>0.0775</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.08410000000000001</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="W4" s="5" t="n">
         <v>40.85</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>72.03</v>
+        <v>71.78</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>2175</v>
       </c>
       <c r="Z4" s="5" t="n">
-        <v>-41.43</v>
+        <v>-45.83</v>
       </c>
       <c r="AA4" s="5" t="n">
         <v>31.76</v>
@@ -918,317 +918,317 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>ANELE</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>111.4</v>
+        <v>296.75</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.5714</v>
+        <v>0.9286</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7.4</v>
+        <v>122</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>107.8</v>
+        <v>176.5</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-9</v>
+        <v>30.5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>134.7</v>
+        <v>354</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.15</v>
+        <v>0.49</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>-0.1431</v>
+        <v>0.2736</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>136</v>
+        <v>396</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>49.22</v>
+        <v>65.23</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>115.3</v>
+        <v>244</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
       <c r="P5" s="7" t="n">
-        <v>4.2</v>
+        <v>44</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>115.8</v>
+        <v>352.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>136.5</v>
+        <v>311</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>-13.1</v>
+        <v>58.75</v>
       </c>
       <c r="T5" s="7" t="n">
-        <v>10.6</v>
+        <v>22.75</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>0.095</v>
+        <v>0.0767</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>0.1116</v>
+        <v>0.0799</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>16.96</v>
+        <v>53.24</v>
       </c>
       <c r="X5" s="7" t="n">
-        <v>50.44</v>
+        <v>75.05</v>
       </c>
       <c r="Y5" s="7" t="n">
-        <v>135.5</v>
+        <v>253.5</v>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>-59.93</v>
+        <v>-48.06</v>
       </c>
       <c r="AA5" s="7" t="n">
-        <v>23.07</v>
+        <v>47.07</v>
       </c>
       <c r="AB5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>296.75</v>
+        <v>111</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.9286</v>
+        <v>0.5714</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>122</v>
+        <v>7.4</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>176.5</v>
+        <v>107.8</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>30.5</v>
+        <v>-8.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>354</v>
+        <v>134.7</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.49</v>
+        <v>0.15</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2736</v>
+        <v>-0.1462</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>396</v>
+        <v>136</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>65.23</v>
+        <v>48.97</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>244</v>
+        <v>115.3</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="P6" s="5" t="n">
-        <v>44</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>352.5</v>
+        <v>115.7</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>311</v>
+        <v>136.5</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>58.75</v>
+        <v>-13.5</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>22.75</v>
+        <v>10.6</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.0767</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.0799</v>
+        <v>0.112</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>53.24</v>
+        <v>16.96</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>75.06</v>
+        <v>50.41</v>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>253.5</v>
+        <v>135.5</v>
       </c>
       <c r="Z6" s="5" t="n">
-        <v>-48.06</v>
+        <v>-60.9</v>
       </c>
       <c r="AA6" s="5" t="n">
-        <v>47.07</v>
+        <v>23.07</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>1694</v>
+          <t>PRZMA</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>68</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.2857</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-291</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>1657</v>
+        <v>2.3</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>60.4</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-452</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>2658</v>
+        <v>-2.35</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>74.8</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.61</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>-0.3251</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>2708</v>
+        <v>-0.07480000000000001</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>77.09999999999999</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>44.87</v>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>1932</v>
+        <v>51.97</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>70.15000000000001</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>Al</t>
-        </is>
-      </c>
       <c r="P7" s="7" t="n">
-        <v>-15</v>
-      </c>
-      <c r="Q7" s="9" t="n">
-        <v>1358</v>
-      </c>
-      <c r="R7" s="9" t="n">
-        <v>2231</v>
+        <v>2</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>78.45</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>-667</v>
+        <v>-7.5</v>
       </c>
       <c r="T7" s="7" t="n">
-        <v>164</v>
+        <v>5.2</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0766</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>41.03</v>
+        <v>29.15</v>
       </c>
       <c r="X7" s="7" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="Y7" s="9" t="n">
-        <v>2276</v>
+        <v>50.14</v>
+      </c>
+      <c r="Y7" s="7" t="n">
+        <v>73.3</v>
       </c>
       <c r="Z7" s="7" t="n">
-        <v>-70.84999999999999</v>
+        <v>-70.54000000000001</v>
       </c>
       <c r="AA7" s="7" t="n">
-        <v>33.84</v>
+        <v>16.76</v>
       </c>
       <c r="AB7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PRZMA</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>67.40000000000001</v>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1694</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.2857</v>
+        <v>0.4286</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>60.4</v>
+        <v>-291</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1657</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>74.84999999999999</v>
+        <v>-452</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>2658</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.083</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>77.09999999999999</v>
+        <v>-0.3251</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>2708</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>70.15000000000001</v>
+        <v>44.87</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>1932</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -1242,44 +1242,44 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P8" s="5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>78.40000000000001</v>
+        <v>-15</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1358</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>2231</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>-8.1</v>
+        <v>-667</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>5.2</v>
+        <v>164</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>29.15</v>
+        <v>41.03</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>50.02</v>
-      </c>
-      <c r="Y8" s="5" t="n">
-        <v>73.3</v>
+        <v>89.75</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>2276</v>
       </c>
       <c r="Z8" s="5" t="n">
-        <v>-75.19</v>
+        <v>-70.84999999999999</v>
       </c>
       <c r="AA8" s="5" t="n">
-        <v>16.76</v>
+        <v>33.84</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
     </row>
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>0.9286</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6.82</v>
+        <v>6.81</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>9.960000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.4245</v>
+        <v>0.3813</v>
       </c>
       <c r="J9" s="7" t="n">
         <v>10.4</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>79.05</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>7.9</v>
+        <v>7.92</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1338,40 +1338,40 @@
         </is>
       </c>
       <c r="P9" s="7" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>10.24</v>
+        <v>10.15</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>8.81</v>
+        <v>8.84</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T9" s="7" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0441</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>0.0317</v>
+        <v>0.0349</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>33.78</v>
+        <v>32.95</v>
       </c>
       <c r="X9" s="7" t="n">
-        <v>79.31999999999999</v>
+        <v>78.03</v>
       </c>
       <c r="Y9" s="7" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="Z9" s="7" t="n">
-        <v>-12.82</v>
+        <v>-20.51</v>
       </c>
       <c r="AA9" s="7" t="n">
-        <v>60.15</v>
+        <v>57.11</v>
       </c>
       <c r="AB9" s="6" t="inlineStr"/>
     </row>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97.3</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.9286</v>
@@ -1397,22 +1397,22 @@
         <v>5.85</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>98.5</v>
+        <v>98.55</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0.11</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.0553</v>
+        <v>0.0559</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>100.3</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>63.66</v>
+        <v>63.75</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>91.90000000000001</v>
+        <v>91.95</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>100.35</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="T10" s="5" t="n">
         <v>4.9</v>
@@ -1454,13 +1454,13 @@
         <v>29.86</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>57.27</v>
+        <v>57.16</v>
       </c>
       <c r="Y10" s="5" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="Z10" s="5" t="n">
-        <v>-18.58</v>
+        <v>-18.27</v>
       </c>
       <c r="AA10" s="5" t="n">
         <v>26.31</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>41.96</v>
+        <v>42.12</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>0</v>
@@ -1486,22 +1486,22 @@
         <v>49.34</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-6.1</v>
+        <v>-6.14</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>61.62</v>
+        <v>61.6</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0.04</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.08109999999999999</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>59.08</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>32.8</v>
+        <v>33.08</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>48.54</v>
@@ -1522,37 +1522,37 @@
         </is>
       </c>
       <c r="P11" s="7" t="n">
-        <v>-2.34</v>
+        <v>-2.32</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>41.08</v>
+        <v>41.12</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>55.04</v>
+        <v>55.06</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>-8.02</v>
+        <v>-7.86</v>
       </c>
       <c r="T11" s="7" t="n">
         <v>3.64</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>0.0868</v>
+        <v>0.08650000000000001</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>0.0973</v>
+        <v>0.0969</v>
       </c>
       <c r="W11" s="7" t="n">
         <v>32.88</v>
       </c>
       <c r="X11" s="7" t="n">
-        <v>23.73</v>
+        <v>23.8</v>
       </c>
       <c r="Y11" s="7" t="n">
         <v>49.66</v>
       </c>
       <c r="Z11" s="7" t="n">
-        <v>-77.11</v>
+        <v>-76.31999999999999</v>
       </c>
       <c r="AA11" s="7" t="n">
         <v>14.11</v>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>127.5</v>
+        <v>126.9</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>126</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>140.5</v>
@@ -1587,13 +1587,13 @@
         <v>-0.12</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.0625</v>
+        <v>-0.0669</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>145.5</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>45.28</v>
+        <v>44.56</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>133.7</v>
@@ -1617,34 +1617,34 @@
         <v>1.3</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>130.4</v>
+        <v>130.3</v>
       </c>
       <c r="R12" s="5" t="n">
         <v>142.5</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>-5.3</v>
+        <v>-5.9</v>
       </c>
       <c r="T12" s="5" t="n">
         <v>5.4</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.0425</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0411</v>
       </c>
       <c r="W12" s="5" t="n">
         <v>18.1</v>
       </c>
       <c r="X12" s="5" t="n">
-        <v>37.08</v>
+        <v>37.03</v>
       </c>
       <c r="Y12" s="5" t="n">
         <v>143.3</v>
       </c>
       <c r="Z12" s="5" t="n">
-        <v>-95.86</v>
+        <v>-99.41</v>
       </c>
       <c r="AA12" s="5" t="n">
         <v>15.94</v>
@@ -1654,184 +1654,184 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>14.59</v>
+        <v>48.6</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-3.1</v>
+        <v>7.12</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>17.65</v>
+        <v>37.94</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1.27</v>
+        <v>6.06</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>14.79</v>
+        <v>49.86</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0799</v>
+        <v>0.1276</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>15.39</v>
+        <v>49.28</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>47.13</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>13.19</v>
+        <v>43.74</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="P13" s="7" t="n">
-        <v>-1.13</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>14.21</v>
+        <v>49.6</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>16.3</v>
+        <v>46.68</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>1.39</v>
+        <v>5.58</v>
       </c>
       <c r="T13" s="7" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0246</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>0.0545</v>
+        <v>0.0296</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>30.36</v>
+        <v>78.98</v>
       </c>
       <c r="X13" s="7" t="n">
-        <v>73.34999999999999</v>
+        <v>73.22</v>
       </c>
       <c r="Y13" s="7" t="n">
-        <v>12.35</v>
+        <v>44.22</v>
       </c>
       <c r="Z13" s="7" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.1</v>
       </c>
       <c r="AA13" s="7" t="n">
-        <v>23.52</v>
+        <v>51.1</v>
       </c>
       <c r="AB13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>48.6</v>
+        <v>14.48</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>7.12</v>
+        <v>-3.1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>37.94</v>
+        <v>17.64</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>6.06</v>
+        <v>1.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>49.86</v>
+        <v>14.77</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.31</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1276</v>
+        <v>0.0718</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>49.28</v>
+        <v>15.39</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>95.18000000000001</v>
+        <v>46.32</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>43.74</v>
+        <v>13.19</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P14" s="5" t="n">
-        <v>3.1</v>
+        <v>-1.14</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>49.6</v>
+        <v>14.18</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>46.68</v>
+        <v>16.29</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>5.58</v>
+        <v>1.28</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.0246</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.0296</v>
+        <v>0.0549</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>78.98</v>
+        <v>30.36</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>73.2</v>
+        <v>73.42</v>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>44.22</v>
+        <v>12.35</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>-8.1</v>
+        <v>-12.64</v>
       </c>
       <c r="AA14" s="5" t="n">
-        <v>51.1</v>
+        <v>23.52</v>
       </c>
       <c r="AB14" s="2" t="inlineStr"/>
     </row>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>750.5</v>
+        <v>754</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>1</v>
@@ -1854,22 +1854,22 @@
         <v>672.5</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>86.5</v>
+        <v>85.5</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>762.5</v>
+        <v>763</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0.19</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.1235</v>
+        <v>0.1287</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>754</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>68.19</v>
+        <v>68.75</v>
       </c>
       <c r="L15" s="7" t="n">
         <v>666</v>
@@ -1881,46 +1881,46 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
           <t>Al</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
         </is>
       </c>
       <c r="P15" s="7" t="n">
         <v>22</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="R15" s="7" t="n">
         <v>739</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>95</v>
+        <v>98.5</v>
       </c>
       <c r="T15" s="7" t="n">
         <v>26</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>0.0345</v>
+        <v>0.0344</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>0.0263</v>
+        <v>0.0261</v>
       </c>
       <c r="W15" s="7" t="n">
         <v>20.99</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>73.86</v>
+        <v>73.94</v>
       </c>
       <c r="Y15" s="7" t="n">
         <v>614.5</v>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>-2.99</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="7" t="n">
         <v>34.77</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>74.25</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1</v>
@@ -1946,25 +1946,25 @@
         <v>85.05</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>19.95</v>
+        <v>20.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>77.90000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1909</v>
+        <v>0.1692</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>79.75</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>55.81</v>
+        <v>54.87</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>62.3</v>
+        <v>62.25</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1982,37 +1982,37 @@
         </is>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-4.7</v>
+        <v>-4.8</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>70.7</v>
+        <v>70.3</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>76.8</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>17.55</v>
+        <v>16.2</v>
       </c>
       <c r="T16" s="5" t="n">
         <v>6.65</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.0667</v>
+        <v>0.0679</v>
       </c>
       <c r="W16" s="5" t="n">
         <v>18.33</v>
       </c>
       <c r="X16" s="5" t="n">
-        <v>57.86</v>
+        <v>58.16</v>
       </c>
       <c r="Y16" s="5" t="n">
         <v>48.8</v>
       </c>
       <c r="Z16" s="5" t="n">
-        <v>-3.1</v>
+        <v>-8.02</v>
       </c>
       <c r="AA16" s="5" t="n">
         <v>38.13</v>
@@ -2098,7 +2098,7 @@
         <v>22.3</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>27.81</v>
+        <v>27.88</v>
       </c>
       <c r="Y17" s="7" t="n">
         <v>31.6</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>10.84</v>
+        <v>10.81</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0</v>
@@ -2130,22 +2130,22 @@
         <v>11.52</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-1.85</v>
+        <v>-1.84</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>14.11</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.1383</v>
+        <v>-0.1407</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>14.03</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>37.2</v>
+        <v>36.92</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>12.67</v>
@@ -2169,34 +2169,34 @@
         <v>-0.13</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>10.86</v>
+        <v>10.85</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>12.92</v>
+        <v>12.91</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>-2.26</v>
+        <v>-2.29</v>
       </c>
       <c r="T18" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.0521</v>
+        <v>0.0522</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.0454</v>
+        <v>0.0455</v>
       </c>
       <c r="W18" s="5" t="n">
         <v>30.12</v>
       </c>
       <c r="X18" s="5" t="n">
-        <v>19.03</v>
+        <v>19.01</v>
       </c>
       <c r="Y18" s="5" t="n">
         <v>12.38</v>
       </c>
       <c r="Z18" s="5" t="n">
-        <v>-91.64</v>
+        <v>-92.73</v>
       </c>
       <c r="AA18" s="5" t="n">
         <v>16.63</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>44.2</v>
+        <v>44.5</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>1</v>
@@ -2222,25 +2222,25 @@
         <v>39.14</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7.7</v>
+        <v>7.62</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>45.18</v>
+        <v>45.26</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0.2</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.2312</v>
+        <v>0.2396</v>
       </c>
       <c r="J19" s="7" t="n">
         <v>46</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>67.5</v>
+        <v>68.16</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>37.62</v>
+        <v>37.64</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
@@ -2258,37 +2258,37 @@
         </is>
       </c>
       <c r="P19" s="7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>43.78</v>
+        <v>43.88</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>44.82</v>
+        <v>44.86</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>7.58</v>
+        <v>7.88</v>
       </c>
       <c r="T19" s="7" t="n">
         <v>2.5</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>0.0567</v>
+        <v>0.0563</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>0.0558</v>
+        <v>0.0554</v>
       </c>
       <c r="W19" s="7" t="n">
         <v>20.47</v>
       </c>
       <c r="X19" s="7" t="n">
-        <v>80.43000000000001</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="Y19" s="7" t="n">
         <v>34.44</v>
       </c>
       <c r="Z19" s="7" t="n">
-        <v>-13.64</v>
+        <v>-11.36</v>
       </c>
       <c r="AA19" s="7" t="n">
         <v>29.59</v>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>215.1</v>
+        <v>213.1</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.07139999999999999</v>
@@ -2314,25 +2314,25 @@
         <v>183</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-11.2</v>
+        <v>-10.6</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>260.8</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0959</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>278</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>51.85</v>
+        <v>50.88</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>222.3</v>
+        <v>222.2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -2346,41 +2346,41 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P20" s="5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>208.9</v>
+        <v>208.3</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>248.4</v>
+        <v>248.2</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>-23.2</v>
+        <v>-25.2</v>
       </c>
       <c r="T20" s="5" t="n">
         <v>15.9</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.0737</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.083</v>
+        <v>0.0837</v>
       </c>
       <c r="W20" s="5" t="n">
         <v>29.36</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>18.69</v>
+        <v>17.12</v>
       </c>
       <c r="Y20" s="5" t="n">
         <v>259.7</v>
       </c>
       <c r="Z20" s="5" t="n">
-        <v>-78.63</v>
+        <v>-81.13</v>
       </c>
       <c r="AA20" s="5" t="n">
         <v>19.32</v>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>0.5714</v>
@@ -2415,13 +2415,13 @@
         <v>-0.05</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0111</v>
+        <v>0.0116</v>
       </c>
       <c r="J21" s="9" t="n">
         <v>1920</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>57.62</v>
+        <v>57.71</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>1714</v>
@@ -2445,13 +2445,13 @@
         <v>68</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>1957</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T21" s="7" t="n">
         <v>97</v>
@@ -2466,13 +2466,13 @@
         <v>11.3</v>
       </c>
       <c r="X21" s="7" t="n">
-        <v>85.23999999999999</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>1644</v>
       </c>
       <c r="Z21" s="7" t="n">
-        <v>-31.48</v>
+        <v>-31.15</v>
       </c>
       <c r="AA21" s="7" t="n">
         <v>18.5</v>
@@ -2568,41 +2568,41 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>CELHA</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>25.48</v>
+        <v>84.5</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>0.9286</v>
+        <v>0.8571</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>4.02</v>
+        <v>0.7</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>20.18</v>
+        <v>78.95</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1.96</v>
+        <v>5.1</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>26.9</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>27.82</v>
+        <v>92.5</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>62.09</v>
+        <v>55.02</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>24.46</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -2611,90 +2611,90 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
       <c r="P23" s="7" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>26.32</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>27.74</v>
+        <v>92.8</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>0.98</v>
+        <v>3.8</v>
       </c>
       <c r="T23" s="7" t="n">
-        <v>1.94</v>
+        <v>5.25</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>0.0761</v>
+        <v>0.062</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>0.0721</v>
+        <v>0.0655</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>36.2</v>
+        <v>19.47</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>69.79000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="Y23" s="7" t="n">
-        <v>22.86</v>
+        <v>77.5</v>
       </c>
       <c r="Z23" s="7" t="n">
-        <v>-41.94</v>
+        <v>-44.57</v>
       </c>
       <c r="AA23" s="7" t="n">
-        <v>24.13</v>
+        <v>25.87</v>
       </c>
       <c r="AB23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MARKA</t>
+          <t>CELHA</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.8571</v>
+        <v>0.9286</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.7</v>
+        <v>4.02</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>78.95</v>
+        <v>20.18</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>89.05</v>
+        <v>26.9</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.0717</v>
+        <v>0.07629999999999999</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>92.5</v>
+        <v>27.82</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>54.85</v>
+        <v>61.65</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>81.84999999999999</v>
+        <v>24.46</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -2703,49 +2703,49 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>88.59999999999999</v>
+        <v>26.3</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>92.75</v>
+        <v>27.74</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>5.25</v>
+        <v>1.94</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.062</v>
+        <v>0.07629999999999999</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="W24" s="5" t="n">
-        <v>19.47</v>
+        <v>36.2</v>
       </c>
       <c r="X24" s="5" t="n">
-        <v>74.45</v>
+        <v>69.59</v>
       </c>
       <c r="Y24" s="5" t="n">
-        <v>77.5</v>
+        <v>22.86</v>
       </c>
       <c r="Z24" s="5" t="n">
-        <v>-45.13</v>
+        <v>-43.37</v>
       </c>
       <c r="AA24" s="5" t="n">
-        <v>25.87</v>
+        <v>24.13</v>
       </c>
       <c r="AB24" s="2" t="inlineStr"/>
     </row>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>76.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
         <v>91</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-6.25</v>
+        <v>-6.3</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>95.84999999999999</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>-0.07919999999999999</v>
+        <v>-0.0774</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>39.88</v>
+        <v>40.1</v>
       </c>
       <c r="L25" s="7" t="n">
         <v>84.55</v>
@@ -2807,34 +2807,34 @@
         <v>-3.95</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>75.59999999999999</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>94.40000000000001</v>
+        <v>94.45</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>-10.3</v>
+        <v>-10.15</v>
       </c>
       <c r="T25" s="7" t="n">
         <v>6.4</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>0.0833</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>0.0746</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="W25" s="7" t="n">
         <v>10.51</v>
       </c>
       <c r="X25" s="7" t="n">
-        <v>24.73</v>
+        <v>24.68</v>
       </c>
       <c r="Y25" s="7" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="Z25" s="7" t="n">
-        <v>-91.51000000000001</v>
+        <v>-90.8</v>
       </c>
       <c r="AA25" s="7" t="n">
         <v>20.99</v>
@@ -2920,7 +2920,7 @@
         <v>12.91</v>
       </c>
       <c r="X26" s="5" t="n">
-        <v>57.54</v>
+        <v>57.32</v>
       </c>
       <c r="Y26" s="5" t="n">
         <v>10.03</v>
@@ -2936,92 +2936,92 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>KARTN</t>
+          <t>MOGAN</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>191</v>
+        <v>21.58</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>15.8</v>
+        <v>2.32</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>164.6</v>
+        <v>15.1</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-27.9</v>
+        <v>4.86</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>240.4</v>
+        <v>20.96</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>-0.1016</v>
+        <v>0.224</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>238.3</v>
+        <v>21.62</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>49.57</v>
+        <v>75.36</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>207.4</v>
+        <v>18.12</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>Al</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>Al</t>
-        </is>
-      </c>
       <c r="P27" s="7" t="n">
-        <v>9.9</v>
+        <v>1.2</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>183</v>
+        <v>20.38</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>229.6</v>
+        <v>20.02</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>-21.9</v>
+        <v>3.76</v>
       </c>
       <c r="T27" s="7" t="n">
-        <v>15.2</v>
+        <v>1.18</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>0.0796</v>
+        <v>0.0551</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>0.0843</v>
+        <v>0.0561</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>49.12</v>
+        <v>31.82</v>
       </c>
       <c r="X27" s="7" t="n">
-        <v>39.39</v>
+        <v>70.14</v>
       </c>
       <c r="Y27" s="7" t="n">
-        <v>228.7</v>
+        <v>16.24</v>
       </c>
       <c r="Z27" s="7" t="n">
-        <v>-74.72</v>
+        <v>-0.73</v>
       </c>
       <c r="AA27" s="7" t="n">
-        <v>20.99</v>
+        <v>41.6</v>
       </c>
       <c r="AB27" s="6" t="inlineStr"/>
     </row>
@@ -3104,7 +3104,7 @@
         <v>16.41</v>
       </c>
       <c r="X28" s="5" t="n">
-        <v>49.08</v>
+        <v>49.02</v>
       </c>
       <c r="Y28" s="5" t="n">
         <v>141.9</v>
@@ -3120,142 +3120,142 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>EUKYO</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>12.81</v>
+        <v>194.6</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>0.1429</v>
+        <v>1</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.82</v>
+        <v>24.6</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>11.47</v>
+        <v>144.1</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>0.1</v>
+        <v>54.2</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>13.63</v>
+        <v>182.2</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>-0.0123</v>
+        <v>0.2973</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>14.4</v>
+        <v>195.5</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>55.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>12.98</v>
+        <v>156.6</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
       <c r="P29" s="7" t="n">
-        <v>0.42</v>
+        <v>10.4</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>13.01</v>
+        <v>187</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>14.21</v>
+        <v>172.8</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>-0.14</v>
+        <v>48.7</v>
       </c>
       <c r="T29" s="7" t="n">
-        <v>0.7</v>
+        <v>7.8</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>0.055</v>
+        <v>0.04</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>0.057</v>
+        <v>0.0367</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>63.52</v>
+        <v>26.31</v>
       </c>
       <c r="X29" s="7" t="n">
-        <v>57.94</v>
+        <v>87.64</v>
       </c>
       <c r="Y29" s="7" t="n">
-        <v>14.15</v>
+        <v>156.4</v>
       </c>
       <c r="Z29" s="7" t="n">
-        <v>-88.33</v>
+        <v>-1.69</v>
       </c>
       <c r="AA29" s="7" t="n">
-        <v>24.86</v>
+        <v>49.79</v>
       </c>
       <c r="AB29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>KARTN</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>192.8</v>
+        <v>189.2</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>24.6</v>
+        <v>15.8</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>144.1</v>
+        <v>164.5</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>54.7</v>
+        <v>-27.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>181.6</v>
+        <v>240.5</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2853</v>
+        <v>-0.1101</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>195.5</v>
+        <v>238.3</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>85.73</v>
+        <v>48.74</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>156.3</v>
+        <v>207.4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3264,90 +3264,90 @@
         </is>
       </c>
       <c r="P30" s="5" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>186.4</v>
+        <v>182.5</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>172.7</v>
+        <v>229.5</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>46.9</v>
+        <v>-23.7</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>7.8</v>
+        <v>15.2</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.0404</v>
+        <v>0.08039999999999999</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.0371</v>
+        <v>0.0851</v>
       </c>
       <c r="W30" s="5" t="n">
-        <v>26.31</v>
+        <v>49.12</v>
       </c>
       <c r="X30" s="5" t="n">
-        <v>87.55</v>
+        <v>39.47</v>
       </c>
       <c r="Y30" s="5" t="n">
-        <v>156.4</v>
+        <v>228.7</v>
       </c>
       <c r="Z30" s="5" t="n">
-        <v>-5.07</v>
+        <v>-77.56999999999999</v>
       </c>
       <c r="AA30" s="5" t="n">
-        <v>49.79</v>
+        <v>20.99</v>
       </c>
       <c r="AB30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>EUKYO</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>196.4</v>
+        <v>12.78</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.1429</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>4.6</v>
+        <v>0.82</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>170.2</v>
+        <v>11.47</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>12.5</v>
+        <v>0.11</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>214.3</v>
+        <v>13.63</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.21</v>
+        <v>0.24</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>-0.0339</v>
+        <v>-0.0146</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>211.2</v>
+        <v>14.4</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>57.7</v>
+        <v>55.1</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>190.9</v>
+        <v>12.98</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
@@ -3356,81 +3356,81 @@
         </is>
       </c>
       <c r="P31" s="7" t="n">
-        <v>6</v>
+        <v>0.42</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>189.6</v>
+        <v>13</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>211.9</v>
+        <v>14.21</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>-5.6</v>
+        <v>-0.17</v>
       </c>
       <c r="T31" s="7" t="n">
-        <v>10.6</v>
+        <v>0.7</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.0551</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>31.69</v>
+        <v>63.52</v>
       </c>
       <c r="X31" s="7" t="n">
-        <v>51.43</v>
+        <v>57.92</v>
       </c>
       <c r="Y31" s="7" t="n">
-        <v>206.6</v>
+        <v>14.15</v>
       </c>
       <c r="Z31" s="7" t="n">
-        <v>-41.81</v>
+        <v>-90</v>
       </c>
       <c r="AA31" s="7" t="n">
-        <v>23.37</v>
+        <v>24.86</v>
       </c>
       <c r="AB31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>92.05</v>
+        <v>196</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2143</v>
+        <v>0.4286</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0.45</v>
+        <v>4.6</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>89.09999999999999</v>
+        <v>170.2</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>1.9</v>
+        <v>12.6</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>103.35</v>
+        <v>214.2</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>-0.16</v>
+        <v>-0.21</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.0832</v>
+        <v>-0.0359</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>108.6</v>
+        <v>211.2</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>52.88</v>
+        <v>57.37</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>93.7</v>
+        <v>190.9</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -3444,159 +3444,177 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="P32" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>91.84999999999999</v>
+        <v>189.5</v>
       </c>
       <c r="R32" s="5" t="n">
-        <v>101</v>
+        <v>211.8</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>5.4</v>
+        <v>10.6</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.05860000000000001</v>
+        <v>0.0541</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.062</v>
+        <v>0.0544</v>
       </c>
       <c r="W32" s="5" t="n">
-        <v>22.07</v>
+        <v>31.69</v>
       </c>
       <c r="X32" s="5" t="n">
-        <v>54.55</v>
+        <v>51.44</v>
       </c>
       <c r="Y32" s="5" t="n">
-        <v>102.95</v>
+        <v>206.6</v>
       </c>
       <c r="Z32" s="5" t="n">
-        <v>-67.41</v>
+        <v>-42.94</v>
       </c>
       <c r="AA32" s="5" t="n">
-        <v>28.01</v>
+        <v>23.37</v>
       </c>
       <c r="AB32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>ISVEA</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>51.65</v>
+        <v>92.25</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
+        <v>0.2143</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>89.09999999999999</v>
+      </c>
       <c r="F33" s="7" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
+        <v>1.85</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>-0.15</v>
+      </c>
       <c r="I33" s="8" t="n">
-        <v>0.1664</v>
-      </c>
-      <c r="J33" s="6" t="inlineStr"/>
+        <v>-0.08119999999999999</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>108.6</v>
+      </c>
       <c r="K33" s="7" t="n">
-        <v>72.67</v>
-      </c>
-      <c r="L33" s="6" t="inlineStr"/>
+        <v>53.1</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>93.7</v>
+      </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr"/>
+      <c r="P33" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="Q33" s="7" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="R33" s="6" t="inlineStr"/>
+        <v>91.95</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>101</v>
+      </c>
       <c r="S33" s="7" t="n">
-        <v>11.4</v>
+        <v>-6.1</v>
       </c>
       <c r="T33" s="7" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0584</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="W33" s="6" t="inlineStr"/>
+        <v>0.0619</v>
+      </c>
+      <c r="W33" s="7" t="n">
+        <v>22.07</v>
+      </c>
       <c r="X33" s="7" t="n">
-        <v>57.35</v>
+        <v>54.6</v>
       </c>
       <c r="Y33" s="7" t="n">
-        <v>42.9</v>
+        <v>102.95</v>
       </c>
       <c r="Z33" s="7" t="n">
-        <v>-21.14</v>
+        <v>-66.59999999999999</v>
       </c>
       <c r="AA33" s="7" t="n">
-        <v>48.41</v>
+        <v>28.01</v>
       </c>
       <c r="AB33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MOGAN</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>20.12</v>
+        <v>170.6</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1</v>
+        <v>0.9286</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2.26</v>
+        <v>12.9</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>15.08</v>
+        <v>144.9</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>4.58</v>
+        <v>10.3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>20.58</v>
+        <v>171.7</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.16</v>
+        <v>-0.21</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1412</v>
+        <v>0.039</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>20.92</v>
+        <v>173</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>70.58</v>
+        <v>77.56</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>18.02</v>
+        <v>163</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -3610,94 +3628,82 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="P34" s="5" t="n">
-        <v>1.08</v>
+        <v>7</v>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>19.94</v>
+        <v>171.3</v>
       </c>
       <c r="R34" s="5" t="n">
-        <v>19.74</v>
+        <v>169.6</v>
       </c>
       <c r="S34" s="5" t="n">
-        <v>2.3</v>
+        <v>10.1</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>1.14</v>
+        <v>3.8</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.0567</v>
+        <v>0.022</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.0209</v>
       </c>
       <c r="W34" s="5" t="n">
-        <v>31.56</v>
+        <v>71.08</v>
       </c>
       <c r="X34" s="5" t="n">
-        <v>69.27</v>
+        <v>69.72</v>
       </c>
       <c r="Y34" s="5" t="n">
-        <v>16.24</v>
+        <v>167.6</v>
       </c>
       <c r="Z34" s="5" t="n">
-        <v>-16.81</v>
+        <v>-14.12</v>
       </c>
       <c r="AA34" s="5" t="n">
-        <v>39.04</v>
+        <v>32.11</v>
       </c>
       <c r="AB34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>ISVEA</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>170.5</v>
+        <v>50.35</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>0.9286</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>144.9</v>
-      </c>
+        <v>0.8571</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
       <c r="F35" s="7" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>171.7</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>-0.21</v>
-      </c>
+        <v>19.3</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" s="8" t="n">
-        <v>0.0384</v>
-      </c>
-      <c r="J35" s="7" t="n">
-        <v>173</v>
-      </c>
+        <v>0.1371</v>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
       <c r="K35" s="7" t="n">
-        <v>77.23</v>
-      </c>
-      <c r="L35" s="7" t="n">
-        <v>163</v>
-      </c>
+        <v>70.75</v>
+      </c>
+      <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -3705,41 +3711,35 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="P35" s="7" t="n">
-        <v>7</v>
-      </c>
+      <c r="P35" s="6" t="inlineStr"/>
       <c r="Q35" s="7" t="n">
-        <v>171.2</v>
-      </c>
-      <c r="R35" s="7" t="n">
-        <v>169.6</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="R35" s="6" t="inlineStr"/>
       <c r="S35" s="7" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="T35" s="7" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>0.022</v>
+        <v>0.0906</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="W35" s="7" t="n">
-        <v>71.08</v>
-      </c>
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="W35" s="6" t="inlineStr"/>
       <c r="X35" s="7" t="n">
-        <v>69.70999999999999</v>
+        <v>57.45</v>
       </c>
       <c r="Y35" s="7" t="n">
-        <v>167.6</v>
+        <v>42.9</v>
       </c>
       <c r="Z35" s="7" t="n">
-        <v>-14.71</v>
+        <v>-25.65</v>
       </c>
       <c r="AA35" s="7" t="n">
-        <v>32.11</v>
+        <v>47.9</v>
       </c>
       <c r="AB35" s="6" t="inlineStr"/>
     </row>
@@ -3750,19 +3750,19 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>39.36</v>
+        <v>39.24</v>
       </c>
       <c r="C36" s="4" t="n">
         <v>0.4286</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>-2.18</v>
+        <v>-2.2</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>43.48</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.82</v>
+        <v>-0.96</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>44.12</v>
@@ -3771,16 +3771,16 @@
         <v>-0.13</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>-0.0619</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>46.16</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>46</v>
+        <v>45.74</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>41.14</v>
+        <v>41.12</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -3801,37 +3801,37 @@
         <v>-0.62</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>39.16</v>
+        <v>39.12</v>
       </c>
       <c r="R36" s="5" t="n">
-        <v>45.92</v>
+        <v>45.94</v>
       </c>
       <c r="S36" s="5" t="n">
-        <v>-3.76</v>
+        <v>-3.88</v>
       </c>
       <c r="T36" s="5" t="n">
         <v>2.68</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>0.0679</v>
+        <v>0.0684</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>0.0697</v>
+        <v>0.0703</v>
       </c>
       <c r="W36" s="5" t="n">
-        <v>15.09</v>
+        <v>14.99</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>58.45</v>
+        <v>58.3</v>
       </c>
       <c r="Y36" s="5" t="n">
         <v>44.06</v>
       </c>
       <c r="Z36" s="5" t="n">
-        <v>-79.79000000000001</v>
+        <v>-81.2</v>
       </c>
       <c r="AA36" s="5" t="n">
-        <v>19.16</v>
+        <v>19.06</v>
       </c>
       <c r="AB36" s="2" t="inlineStr"/>
     </row>
@@ -3914,7 +3914,7 @@
         <v>18.58</v>
       </c>
       <c r="X37" s="7" t="n">
-        <v>91.63</v>
+        <v>91.64</v>
       </c>
       <c r="Y37" s="7" t="n">
         <v>467</v>
@@ -3930,184 +3930,184 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>KOCMT</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>0.5714</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>-0.8</v>
+        <v>1.1</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>6.13</v>
+        <v>3.81</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.28</v>
+        <v>0.71</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>6.46</v>
+        <v>6.19</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>-0.18</v>
+        <v>-0.06</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-0.0435</v>
+        <v>0.1493</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>6.54</v>
+        <v>6.18</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>41.71</v>
+        <v>69.37</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>5.93</v>
+        <v>4.75</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Güçlü sat</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Güçlü sat</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P38" s="5" t="n">
-        <v>-0.23</v>
+        <v>0.51</v>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>5.57</v>
+        <v>5.51</v>
       </c>
       <c r="R38" s="5" t="n">
-        <v>6.51</v>
+        <v>5.83</v>
       </c>
       <c r="S38" s="5" t="n">
-        <v>-0.43</v>
+        <v>0.87</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.0692</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.0526</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="W38" s="5" t="n">
-        <v>11.98</v>
+        <v>48.84</v>
       </c>
       <c r="X38" s="5" t="n">
-        <v>33.82</v>
+        <v>67.53</v>
       </c>
       <c r="Y38" s="5" t="n">
-        <v>5.34</v>
+        <v>4.8</v>
       </c>
       <c r="Z38" s="5" t="n">
-        <v>-80</v>
+        <v>-25.45</v>
       </c>
       <c r="AA38" s="5" t="n">
-        <v>16.9</v>
+        <v>30.37</v>
       </c>
       <c r="AB38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>KOCMT</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>5.62</v>
+        <v>5.48</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>0.5714</v>
+        <v>0</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3.81</v>
+        <v>6.13</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.71</v>
+        <v>-0.27</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>6.19</v>
+        <v>6.46</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.06</v>
+        <v>-0.18</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.1493</v>
+        <v>-0.047</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>6.18</v>
+        <v>6.54</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>69.37</v>
+        <v>41.4</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>4.75</v>
+        <v>5.92</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Güçlü sat</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Güçlü sat</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0.51</v>
+        <v>-0.23</v>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>5.51</v>
+        <v>5.57</v>
       </c>
       <c r="R39" s="7" t="n">
-        <v>5.83</v>
+        <v>6.51</v>
       </c>
       <c r="S39" s="7" t="n">
-        <v>0.87</v>
+        <v>-0.45</v>
       </c>
       <c r="T39" s="7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>0.07429999999999999</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0528</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>48.84</v>
+        <v>11.98</v>
       </c>
       <c r="X39" s="7" t="n">
-        <v>67.40000000000001</v>
+        <v>33.68</v>
       </c>
       <c r="Y39" s="7" t="n">
-        <v>4.8</v>
+        <v>5.34</v>
       </c>
       <c r="Z39" s="7" t="n">
-        <v>-25.45</v>
+        <v>-82.11</v>
       </c>
       <c r="AA39" s="7" t="n">
-        <v>30.37</v>
+        <v>16.9</v>
       </c>
       <c r="AB39" s="6" t="inlineStr"/>
     </row>
@@ -4190,7 +4190,7 @@
         <v>14.76</v>
       </c>
       <c r="X40" s="5" t="n">
-        <v>58.04</v>
+        <v>58.1</v>
       </c>
       <c r="Y40" s="5" t="n">
         <v>6.12</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>317.25</v>
+        <v>317.5</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>1</v>
@@ -4222,7 +4222,7 @@
         <v>303.75</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>30</v>
+        <v>29.75</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>328.75</v>
@@ -4231,13 +4231,13 @@
         <v>0.01</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0682</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J41" s="7" t="n">
         <v>330.75</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>57.26</v>
+        <v>57.34</v>
       </c>
       <c r="L41" s="7" t="n">
         <v>302.25</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
@@ -4267,7 +4267,7 @@
         <v>329.25</v>
       </c>
       <c r="S41" s="7" t="n">
-        <v>10.25</v>
+        <v>10.5</v>
       </c>
       <c r="T41" s="7" t="n">
         <v>15.5</v>
@@ -4282,13 +4282,13 @@
         <v>12.79</v>
       </c>
       <c r="X41" s="7" t="n">
-        <v>49.53</v>
+        <v>49.71</v>
       </c>
       <c r="Y41" s="7" t="n">
         <v>272.75</v>
       </c>
       <c r="Z41" s="7" t="n">
-        <v>-7.18</v>
+        <v>-6.67</v>
       </c>
       <c r="AA41" s="7" t="n">
         <v>26.25</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>0</v>
@@ -4323,16 +4323,16 @@
         <v>-0.23</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-0.145</v>
+        <v>-0.1455</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>3913</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>29.01</v>
+        <v>28.96</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>2510</v>
       </c>
       <c r="S42" s="5" t="n">
-        <v>-349</v>
+        <v>-350</v>
       </c>
       <c r="T42" s="5" t="n">
         <v>177</v>
@@ -4374,13 +4374,13 @@
         <v>53.72</v>
       </c>
       <c r="X42" s="5" t="n">
-        <v>12.96</v>
+        <v>13.02</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>1884</v>
       </c>
       <c r="Z42" s="5" t="n">
-        <v>-80.3</v>
+        <v>-80.41</v>
       </c>
       <c r="AA42" s="5" t="n">
         <v>14.16</v>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>18.7</v>
+        <v>18.78</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>0.2143</v>
@@ -4406,25 +4406,25 @@
         <v>17.97</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>19.54</v>
+        <v>19.55</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0032</v>
+        <v>0.0075</v>
       </c>
       <c r="J43" s="7" t="n">
         <v>20.32</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>54.02</v>
+        <v>54.67</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>18.25</v>
+        <v>18.26</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -4442,37 +4442,37 @@
         </is>
       </c>
       <c r="P43" s="7" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Q43" s="7" t="n">
-        <v>18.86</v>
+        <v>18.88</v>
       </c>
       <c r="R43" s="7" t="n">
-        <v>20.52</v>
+        <v>20.53</v>
       </c>
       <c r="S43" s="7" t="n">
-        <v>-0.2</v>
+        <v>-0.12</v>
       </c>
       <c r="T43" s="7" t="n">
         <v>1.2</v>
       </c>
       <c r="U43" s="8" t="n">
-        <v>0.0639</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V43" s="8" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.0682</v>
       </c>
       <c r="W43" s="7" t="n">
         <v>14.46</v>
       </c>
       <c r="X43" s="7" t="n">
-        <v>65.5</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="Y43" s="7" t="n">
         <v>19.87</v>
       </c>
       <c r="Z43" s="7" t="n">
-        <v>-34.91</v>
+        <v>-33.19</v>
       </c>
       <c r="AA43" s="7" t="n">
         <v>25.85</v>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>39.1</v>
+        <v>39.32</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>0.9286</v>
@@ -4498,25 +4498,25 @@
         <v>31.62</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>39.14</v>
+        <v>39.18</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>0.17</v>
+        <v>0.1765</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>41.68</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>70.41</v>
+        <v>71.48</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>34.06</v>
+        <v>34.08</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -4534,37 +4534,37 @@
         </is>
       </c>
       <c r="P44" s="5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>39.6</v>
+        <v>39.66</v>
       </c>
       <c r="R44" s="5" t="n">
-        <v>38.44</v>
+        <v>38.46</v>
       </c>
       <c r="S44" s="5" t="n">
-        <v>8.18</v>
+        <v>8.4</v>
       </c>
       <c r="T44" s="5" t="n">
         <v>1.96</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>0.0503</v>
+        <v>0.05</v>
       </c>
       <c r="V44" s="4" t="n">
-        <v>0.059</v>
+        <v>0.0587</v>
       </c>
       <c r="W44" s="5" t="n">
         <v>25.1</v>
       </c>
       <c r="X44" s="5" t="n">
-        <v>74.95999999999999</v>
+        <v>74.86</v>
       </c>
       <c r="Y44" s="5" t="n">
         <v>34.52</v>
       </c>
       <c r="Z44" s="5" t="n">
-        <v>-22.2</v>
+        <v>-20.31</v>
       </c>
       <c r="AA44" s="5" t="n">
         <v>40.4</v>
@@ -4574,92 +4574,92 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>AKSUE</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>79.2</v>
+        <v>43.6</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-1.2</v>
+        <v>1.12</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>66.75</v>
+        <v>41.12</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>6.5</v>
+        <v>-1.46</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>86.5</v>
+        <v>48.76</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0902</v>
+        <v>-0.0599</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>88.90000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>58.22</v>
+        <v>48.85</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>74.55</v>
+        <v>45.32</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="P45" s="7" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="Q45" s="7" t="n">
-        <v>78.09999999999999</v>
+        <v>44.48</v>
       </c>
       <c r="R45" s="7" t="n">
-        <v>81.59999999999999</v>
+        <v>50.22</v>
       </c>
       <c r="S45" s="7" t="n">
-        <v>-0.7</v>
+        <v>-3.4</v>
       </c>
       <c r="T45" s="7" t="n">
-        <v>4.95</v>
+        <v>2.6</v>
       </c>
       <c r="U45" s="8" t="n">
-        <v>0.06280000000000001</v>
+        <v>0.0595</v>
       </c>
       <c r="V45" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0636</v>
       </c>
       <c r="W45" s="7" t="n">
-        <v>15.76</v>
+        <v>28.38</v>
       </c>
       <c r="X45" s="7" t="n">
-        <v>67.26000000000001</v>
+        <v>58.11</v>
       </c>
       <c r="Y45" s="7" t="n">
-        <v>61.75</v>
+        <v>49.22</v>
       </c>
       <c r="Z45" s="7" t="n">
-        <v>-3.94</v>
+        <v>-73.28</v>
       </c>
       <c r="AA45" s="7" t="n">
-        <v>40.35</v>
+        <v>22.83</v>
       </c>
       <c r="AB45" s="6" t="inlineStr"/>
     </row>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>14.03</v>
+        <v>13.89</v>
       </c>
       <c r="C46" s="4" t="n">
         <v>0.2143</v>
@@ -4679,28 +4679,28 @@
         <v>-1.16</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>13.71</v>
+        <v>13.7</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>15.39</v>
+        <v>15.38</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>0.0447</v>
+        <v>0.0343</v>
       </c>
       <c r="J46" s="5" t="n">
         <v>15.9</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>56.17</v>
+        <v>54.99</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>13.69</v>
+        <v>13.68</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4718,37 +4718,37 @@
         </is>
       </c>
       <c r="P46" s="5" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>13</v>
+        <v>12.96</v>
       </c>
       <c r="R46" s="5" t="n">
-        <v>14.99</v>
+        <v>14.98</v>
       </c>
       <c r="S46" s="5" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="T46" s="5" t="n">
         <v>0.84</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.0601</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.0608</v>
       </c>
       <c r="W46" s="5" t="n">
         <v>19.67</v>
       </c>
       <c r="X46" s="5" t="n">
-        <v>32.65</v>
+        <v>33.07</v>
       </c>
       <c r="Y46" s="5" t="n">
         <v>11.9</v>
       </c>
       <c r="Z46" s="5" t="n">
-        <v>-46.75</v>
+        <v>-50.25</v>
       </c>
       <c r="AA46" s="5" t="n">
         <v>26.41</v>
@@ -4758,92 +4758,92 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>AKSUE</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>43.18</v>
+        <v>78</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1.12</v>
+        <v>-1.2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>41.12</v>
+        <v>66.75</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-1.34</v>
+        <v>6.85</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>48.8</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>51.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>47.87</v>
+        <v>57.24</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>45.3</v>
+        <v>74.45</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O47" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P47" s="7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>44.36</v>
+        <v>77.75</v>
       </c>
       <c r="R47" s="7" t="n">
-        <v>50.18</v>
+        <v>81.45</v>
       </c>
       <c r="S47" s="7" t="n">
-        <v>-3.82</v>
+        <v>-1.9</v>
       </c>
       <c r="T47" s="7" t="n">
-        <v>2.6</v>
+        <v>4.95</v>
       </c>
       <c r="U47" s="8" t="n">
-        <v>0.0601</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V47" s="8" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0393</v>
       </c>
       <c r="W47" s="7" t="n">
-        <v>28.38</v>
+        <v>15.76</v>
       </c>
       <c r="X47" s="7" t="n">
-        <v>58.38</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="Y47" s="7" t="n">
-        <v>49.22</v>
+        <v>61.75</v>
       </c>
       <c r="Z47" s="7" t="n">
-        <v>-77.18000000000001</v>
+        <v>-10.24</v>
       </c>
       <c r="AA47" s="7" t="n">
-        <v>22.83</v>
+        <v>40.35</v>
       </c>
       <c r="AB47" s="6" t="inlineStr"/>
     </row>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>162</v>
+        <v>161.8</v>
       </c>
       <c r="C48" s="4" t="n">
         <v>0.4286</v>
@@ -4866,7 +4866,7 @@
         <v>149.2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>173.6</v>
@@ -4875,13 +4875,13 @@
         <v>0.04</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>-0.0609</v>
+        <v>-0.062</v>
       </c>
       <c r="J48" s="5" t="n">
         <v>177.1</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>53.47</v>
+        <v>53.27</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>164.3</v>
@@ -4908,10 +4908,10 @@
         <v>161.1</v>
       </c>
       <c r="R48" s="5" t="n">
-        <v>174.8</v>
+        <v>174.7</v>
       </c>
       <c r="S48" s="5" t="n">
-        <v>-2.3</v>
+        <v>-2.5</v>
       </c>
       <c r="T48" s="5" t="n">
         <v>7.4</v>
@@ -4926,13 +4926,13 @@
         <v>46.97</v>
       </c>
       <c r="X48" s="5" t="n">
-        <v>72.3</v>
+        <v>72.27</v>
       </c>
       <c r="Y48" s="5" t="n">
         <v>155.7</v>
       </c>
       <c r="Z48" s="5" t="n">
-        <v>-47.62</v>
+        <v>-48.35</v>
       </c>
       <c r="AA48" s="5" t="n">
         <v>26.63</v>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46.2</v>
+        <v>46.26</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>0.2143</v>
@@ -4958,7 +4958,7 @@
         <v>46.06</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>48.16</v>
@@ -4967,13 +4967,13 @@
         <v>0.19</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.014</v>
+        <v>0.0154</v>
       </c>
       <c r="J49" s="7" t="n">
         <v>49.8</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>51.98</v>
+        <v>52.22</v>
       </c>
       <c r="L49" s="7" t="n">
         <v>46.44</v>
@@ -4994,37 +4994,37 @@
         </is>
       </c>
       <c r="P49" s="7" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="Q49" s="7" t="n">
-        <v>45.88</v>
+        <v>45.9</v>
       </c>
       <c r="R49" s="7" t="n">
         <v>49.5</v>
       </c>
       <c r="S49" s="7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T49" s="7" t="n">
         <v>1.92</v>
       </c>
       <c r="U49" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.0414</v>
       </c>
       <c r="V49" s="8" t="n">
-        <v>0.0423</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>14.99</v>
       </c>
       <c r="X49" s="7" t="n">
-        <v>69.13</v>
+        <v>69.17</v>
       </c>
       <c r="Y49" s="7" t="n">
         <v>44.12</v>
       </c>
       <c r="Z49" s="7" t="n">
-        <v>-50.7</v>
+        <v>-49.86</v>
       </c>
       <c r="AA49" s="7" t="n">
         <v>18.97</v>
@@ -5034,50 +5034,50 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>ATSYH</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>29.4</v>
+        <v>110.1</v>
       </c>
       <c r="C50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>-4.5</v>
+        <v>2.2</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>34.4</v>
+        <v>101.6</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.66</v>
+        <v>-6.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>36.22</v>
+        <v>130.1</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.29</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>-0.0898</v>
+        <v>0.0587</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>37.66</v>
+        <v>129</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>42.98</v>
+        <v>49.71</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>32.76</v>
+        <v>113.9</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -5086,357 +5086,357 @@
         </is>
       </c>
       <c r="P50" s="5" t="n">
-        <v>-1.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q50" s="5" t="n">
-        <v>28.04</v>
+        <v>116.7</v>
       </c>
       <c r="R50" s="5" t="n">
-        <v>34.54</v>
+        <v>123.9</v>
       </c>
       <c r="S50" s="5" t="n">
-        <v>-2.42</v>
+        <v>-5.4</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>0.07150000000000001</v>
+        <v>0.0519</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>0.0641</v>
+        <v>0.0415</v>
       </c>
       <c r="W50" s="5" t="n">
-        <v>15.21</v>
+        <v>13.5</v>
       </c>
       <c r="X50" s="5" t="n">
-        <v>25.13</v>
+        <v>23.61</v>
       </c>
       <c r="Y50" s="5" t="n">
-        <v>31.78</v>
+        <v>119</v>
       </c>
       <c r="Z50" s="5" t="n">
-        <v>-76.17</v>
+        <v>-64.78</v>
       </c>
       <c r="AA50" s="5" t="n">
-        <v>20.96</v>
+        <v>35.38</v>
       </c>
       <c r="AB50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>ATSYH</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>110.1</v>
+        <v>29.28</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>2.2</v>
+        <v>-4.5</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>101.6</v>
+        <v>34.4</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-6.3</v>
+        <v>-0.62</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>130.1</v>
+        <v>36.22</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.3</v>
+        <v>-0.06</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0587</v>
+        <v>-0.0935</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>129</v>
+        <v>37.66</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>49.71</v>
+        <v>42.5</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>114</v>
+        <v>32.74</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
+          <t>Güçlü sat</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="N51" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="O51" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
       <c r="P51" s="7" t="n">
-        <v>2.6</v>
+        <v>-1.58</v>
       </c>
       <c r="Q51" s="7" t="n">
-        <v>116.7</v>
+        <v>28</v>
       </c>
       <c r="R51" s="7" t="n">
-        <v>123.9</v>
+        <v>34.52</v>
       </c>
       <c r="S51" s="7" t="n">
-        <v>-5.4</v>
+        <v>-2.54</v>
       </c>
       <c r="T51" s="7" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="U51" s="8" t="n">
-        <v>0.0519</v>
+        <v>0.0718</v>
       </c>
       <c r="V51" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.0644</v>
       </c>
       <c r="W51" s="7" t="n">
-        <v>13.5</v>
+        <v>15.21</v>
       </c>
       <c r="X51" s="7" t="n">
-        <v>23.96</v>
+        <v>25.32</v>
       </c>
       <c r="Y51" s="7" t="n">
-        <v>119</v>
+        <v>31.78</v>
       </c>
       <c r="Z51" s="7" t="n">
-        <v>-64.78</v>
+        <v>-77.34</v>
       </c>
       <c r="AA51" s="7" t="n">
-        <v>35.38</v>
+        <v>20.96</v>
       </c>
       <c r="AB51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>7.36</v>
+        <v>17.95</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1</v>
+        <v>0.4286</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>5.79</v>
+        <v>16.15</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>1.53</v>
+        <v>-0.15</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>7.57</v>
+        <v>19.71</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.11</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.1376</v>
+        <v>-0.0493</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>8.85</v>
+        <v>20</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>62.31</v>
+        <v>51.87</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>6.39</v>
+        <v>18.1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P52" s="5" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>6.83</v>
+        <v>18.08</v>
       </c>
       <c r="R52" s="5" t="n">
-        <v>7.66</v>
+        <v>19.95</v>
       </c>
       <c r="S52" s="5" t="n">
-        <v>0.86</v>
+        <v>0.33</v>
       </c>
       <c r="T52" s="5" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>0.08449999999999999</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="V52" s="4" t="n">
-        <v>0.0727</v>
+        <v>0.0563</v>
       </c>
       <c r="W52" s="5" t="n">
-        <v>21.69</v>
+        <v>11.01</v>
       </c>
       <c r="X52" s="5" t="n">
-        <v>58.88</v>
+        <v>47</v>
       </c>
       <c r="Y52" s="5" t="n">
-        <v>5.4</v>
+        <v>16.35</v>
       </c>
       <c r="Z52" s="5" t="n">
-        <v>-2</v>
+        <v>-53.95</v>
       </c>
       <c r="AA52" s="5" t="n">
-        <v>31.23</v>
+        <v>27.24</v>
       </c>
       <c r="AB52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>IZMDC</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>17.95</v>
+        <v>13.55</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.9286</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.47</v>
+        <v>1.94</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>16.15</v>
+        <v>9.75</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.15</v>
+        <v>2.35</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>19.71</v>
+        <v>14.18</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>-0.0493</v>
+        <v>0.1143</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>20</v>
+        <v>13.87</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>51.87</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>18.11</v>
+        <v>11.9</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="O53" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
       <c r="P53" s="7" t="n">
-        <v>0.42</v>
+        <v>0.96</v>
       </c>
       <c r="Q53" s="7" t="n">
-        <v>18.08</v>
+        <v>13.5</v>
       </c>
       <c r="R53" s="7" t="n">
-        <v>19.95</v>
+        <v>13.48</v>
       </c>
       <c r="S53" s="7" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="T53" s="7" t="n">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U53" s="8" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.0597</v>
       </c>
       <c r="V53" s="8" t="n">
-        <v>0.0563</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="W53" s="7" t="n">
-        <v>11.01</v>
+        <v>44.51</v>
       </c>
       <c r="X53" s="7" t="n">
-        <v>47.48</v>
+        <v>53.88</v>
       </c>
       <c r="Y53" s="7" t="n">
-        <v>16.35</v>
+        <v>10.92</v>
       </c>
       <c r="Z53" s="7" t="n">
-        <v>-53.95</v>
+        <v>-10.26</v>
       </c>
       <c r="AA53" s="7" t="n">
-        <v>27.24</v>
+        <v>40.34</v>
       </c>
       <c r="AB53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>IZMDC</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>13.54</v>
+        <v>7.31</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.9286</v>
+        <v>1</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1.94</v>
+        <v>-0.37</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>9.75</v>
+        <v>5.78</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>14.18</v>
+        <v>7.56</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.29</v>
+        <v>-0.03</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0.1135</v>
+        <v>0.1298</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>13.87</v>
+        <v>8.85</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>69.98999999999999</v>
+        <v>61.89</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>11.9</v>
+        <v>6.39</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -5445,49 +5445,49 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
       <c r="P54" s="5" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="Q54" s="5" t="n">
-        <v>13.49</v>
+        <v>6.81</v>
       </c>
       <c r="R54" s="5" t="n">
-        <v>13.48</v>
+        <v>7.66</v>
       </c>
       <c r="S54" s="5" t="n">
-        <v>0.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>0.0597</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>0.0745</v>
+        <v>0.0737</v>
       </c>
       <c r="W54" s="5" t="n">
-        <v>44.51</v>
+        <v>21.75</v>
       </c>
       <c r="X54" s="5" t="n">
-        <v>53.79</v>
+        <v>59.18</v>
       </c>
       <c r="Y54" s="5" t="n">
-        <v>10.92</v>
+        <v>5.4</v>
       </c>
       <c r="Z54" s="5" t="n">
-        <v>-10.58</v>
+        <v>-6.83</v>
       </c>
       <c r="AA54" s="5" t="n">
-        <v>40.34</v>
+        <v>31.62</v>
       </c>
       <c r="AB54" s="2" t="inlineStr"/>
     </row>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>18.82</v>
+        <v>18.88</v>
       </c>
       <c r="C55" s="8" t="n">
         <v>0.1429</v>
@@ -5507,28 +5507,28 @@
         <v>-0.39</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>18.86</v>
+        <v>18.87</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>19.79</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0043</v>
+        <v>0.0075</v>
       </c>
       <c r="J55" s="7" t="n">
         <v>20.14</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>51.95</v>
+        <v>52.54</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>18.87</v>
+        <v>18.88</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -5546,37 +5546,37 @@
         </is>
       </c>
       <c r="P55" s="7" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q55" s="7" t="n">
-        <v>18.53</v>
+        <v>18.55</v>
       </c>
       <c r="R55" s="7" t="n">
-        <v>20.09</v>
+        <v>20.1</v>
       </c>
       <c r="S55" s="7" t="n">
-        <v>-0.39</v>
+        <v>-0.33</v>
       </c>
       <c r="T55" s="7" t="n">
         <v>0.75</v>
       </c>
       <c r="U55" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0399</v>
       </c>
       <c r="V55" s="8" t="n">
-        <v>0.0393</v>
+        <v>0.0392</v>
       </c>
       <c r="W55" s="7" t="n">
         <v>13.14</v>
       </c>
       <c r="X55" s="7" t="n">
-        <v>59.52</v>
+        <v>59.66</v>
       </c>
       <c r="Y55" s="7" t="n">
         <v>19.52</v>
       </c>
       <c r="Z55" s="7" t="n">
-        <v>-55.93</v>
+        <v>-53.39</v>
       </c>
       <c r="AA55" s="7" t="n">
         <v>18.55</v>
@@ -5586,234 +5586,234 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>DGNMO</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>40.42</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.7857</v>
+        <v>0.8571</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>5.04</v>
+        <v>0.31</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>36.24</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-1.98</v>
+        <v>0.62</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>47.48</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.1903</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>49.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>51.54</v>
+        <v>55.77</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>42.2</v>
+        <v>8.1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Al</t>
-        </is>
-      </c>
       <c r="P56" s="5" t="n">
-        <v>1.84</v>
+        <v>0.05</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>40.54</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R56" s="5" t="n">
-        <v>46.64</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S56" s="5" t="n">
-        <v>-0.86</v>
+        <v>1.01</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>2.72</v>
+        <v>0.49</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>0.0675</v>
+        <v>0.0571</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>0.0837</v>
+        <v>0.0564</v>
       </c>
       <c r="W56" s="5" t="n">
-        <v>50.24</v>
+        <v>18.39</v>
       </c>
       <c r="X56" s="5" t="n">
-        <v>62.48</v>
+        <v>62.73</v>
       </c>
       <c r="Y56" s="5" t="n">
-        <v>49.32</v>
+        <v>7.68</v>
       </c>
       <c r="Z56" s="5" t="n">
-        <v>-86.41</v>
+        <v>-25.91</v>
       </c>
       <c r="AA56" s="5" t="n">
-        <v>30.32</v>
+        <v>25.2</v>
       </c>
       <c r="AB56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>DGNMO</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>8.59</v>
+        <v>118.8</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>0.8571</v>
+        <v>0.1429</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.31</v>
+        <v>-7.8</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>132.1</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.63</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>9.02</v>
+        <v>142.1</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.03</v>
+        <v>-0.28</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.1848</v>
+        <v>-0.0755</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>152.5</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>54.99</v>
+        <v>42.13</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>8.1</v>
+        <v>130.3</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P57" s="7" t="n">
-        <v>0.05</v>
+        <v>-3.4</v>
       </c>
       <c r="Q57" s="7" t="n">
-        <v>8.960000000000001</v>
+        <v>121.4</v>
       </c>
       <c r="R57" s="7" t="n">
-        <v>9.289999999999999</v>
+        <v>140.7</v>
       </c>
       <c r="S57" s="7" t="n">
-        <v>0.97</v>
+        <v>-15.8</v>
       </c>
       <c r="T57" s="7" t="n">
-        <v>0.49</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="U57" s="8" t="n">
-        <v>0.0573</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="V57" s="8" t="n">
-        <v>0.0567</v>
+        <v>0.0684</v>
       </c>
       <c r="W57" s="7" t="n">
-        <v>18.39</v>
+        <v>13.84</v>
       </c>
       <c r="X57" s="7" t="n">
-        <v>63.01</v>
+        <v>61.59</v>
       </c>
       <c r="Y57" s="7" t="n">
-        <v>7.68</v>
+        <v>143.6</v>
       </c>
       <c r="Z57" s="7" t="n">
-        <v>-27.73</v>
+        <v>-86.86</v>
       </c>
       <c r="AA57" s="7" t="n">
-        <v>25.2</v>
+        <v>20.54</v>
       </c>
       <c r="AB57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>118.8</v>
+        <v>40.08</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.1429</v>
+        <v>0.7857</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>-7.8</v>
+        <v>5.04</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>132.1</v>
+        <v>36.24</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-8.199999999999999</v>
+        <v>-1.88</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>142.1</v>
+        <v>47.48</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.06</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>-0.0755</v>
+        <v>-0.002</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>152.5</v>
+        <v>49.7</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>42.13</v>
+        <v>50.79</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>130.3</v>
+        <v>42.18</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -5822,40 +5822,40 @@
         </is>
       </c>
       <c r="P58" s="5" t="n">
-        <v>-3.4</v>
+        <v>1.82</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>121.4</v>
+        <v>40.44</v>
       </c>
       <c r="R58" s="5" t="n">
-        <v>140.7</v>
+        <v>46.6</v>
       </c>
       <c r="S58" s="5" t="n">
-        <v>-15.8</v>
+        <v>-1.2</v>
       </c>
       <c r="T58" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>2.72</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="V58" s="4" t="n">
-        <v>0.0684</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="W58" s="5" t="n">
-        <v>13.84</v>
+        <v>50.24</v>
       </c>
       <c r="X58" s="5" t="n">
-        <v>61.63</v>
+        <v>62.36</v>
       </c>
       <c r="Y58" s="5" t="n">
-        <v>143.6</v>
+        <v>49.32</v>
       </c>
       <c r="Z58" s="5" t="n">
-        <v>-86.86</v>
+        <v>-89.56999999999999</v>
       </c>
       <c r="AA58" s="5" t="n">
-        <v>20.54</v>
+        <v>30.32</v>
       </c>
       <c r="AB58" s="2" t="inlineStr"/>
     </row>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>45.02</v>
+        <v>45.04</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>0</v>
@@ -5878,7 +5878,7 @@
         <v>48.02</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-2.28</v>
+        <v>-2.3</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>50.54</v>
@@ -5887,13 +5887,13 @@
         <v>-0.1</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>-0.0546</v>
+        <v>-0.0542</v>
       </c>
       <c r="J59" s="7" t="n">
         <v>50.96</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>36.29</v>
+        <v>36.44</v>
       </c>
       <c r="L59" s="7" t="n">
         <v>47.36</v>
@@ -5923,7 +5923,7 @@
         <v>49.8</v>
       </c>
       <c r="S59" s="7" t="n">
-        <v>-2.98</v>
+        <v>-2.96</v>
       </c>
       <c r="T59" s="7" t="n">
         <v>1.66</v>
@@ -5938,13 +5938,13 @@
         <v>22.7</v>
       </c>
       <c r="X59" s="7" t="n">
-        <v>13.08</v>
+        <v>13.2</v>
       </c>
       <c r="Y59" s="7" t="n">
         <v>48.2</v>
       </c>
       <c r="Z59" s="7" t="n">
-        <v>-75.45</v>
+        <v>-75.15000000000001</v>
       </c>
       <c r="AA59" s="7" t="n">
         <v>11.42</v>
@@ -5958,37 +5958,37 @@
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>76.84999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.8571</v>
+        <v>1</v>
       </c>
       <c r="D60" s="5" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="F60" s="5" t="n">
         <v>8.9</v>
       </c>
-      <c r="E60" s="5" t="n">
-        <v>64.55</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="G60" s="5" t="n">
-        <v>77</v>
+        <v>77.25</v>
       </c>
       <c r="H60" s="5" t="n">
         <v>0.06</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.1058</v>
+        <v>0.1201</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>77.45</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>65.06999999999999</v>
+        <v>66.23</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>70.05</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -6002,44 +6002,44 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P60" s="5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>78.05</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="R60" s="5" t="n">
-        <v>77.5</v>
+        <v>77.8</v>
       </c>
       <c r="S60" s="5" t="n">
-        <v>5.15</v>
+        <v>6.15</v>
       </c>
       <c r="T60" s="5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>0.0489</v>
+        <v>0.0492</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>0.0466</v>
+        <v>0.0469</v>
       </c>
       <c r="W60" s="5" t="n">
-        <v>45.91</v>
+        <v>46.03</v>
       </c>
       <c r="X60" s="5" t="n">
-        <v>68.33</v>
+        <v>68.58</v>
       </c>
       <c r="Y60" s="5" t="n">
         <v>67.15000000000001</v>
       </c>
       <c r="Z60" s="5" t="n">
-        <v>-5.29</v>
+        <v>-2.08</v>
       </c>
       <c r="AA60" s="5" t="n">
-        <v>29.39</v>
+        <v>30.24</v>
       </c>
       <c r="AB60" s="2" t="inlineStr"/>
     </row>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>25.02</v>
+        <v>25.18</v>
       </c>
       <c r="C61" s="8" t="n">
         <v>0.3571</v>
@@ -6059,25 +6059,25 @@
         <v>0.34</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>22.42</v>
+        <v>22.44</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>25.54</v>
+        <v>25.58</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.0974</v>
+        <v>0.1044</v>
       </c>
       <c r="J61" s="7" t="n">
         <v>26.46</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>57.84</v>
+        <v>58.65</v>
       </c>
       <c r="L61" s="7" t="n">
         <v>23.48</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr">
@@ -6098,37 +6098,37 @@
         </is>
       </c>
       <c r="P61" s="7" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="Q61" s="7" t="n">
-        <v>25.06</v>
+        <v>25.1</v>
       </c>
       <c r="R61" s="7" t="n">
         <v>26.5</v>
       </c>
       <c r="S61" s="7" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="T61" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="U61" s="8" t="n">
-        <v>0.0599</v>
+        <v>0.0595</v>
       </c>
       <c r="V61" s="8" t="n">
-        <v>0.058</v>
+        <v>0.0576</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>29.12</v>
       </c>
       <c r="X61" s="7" t="n">
-        <v>66.31999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="Y61" s="7" t="n">
         <v>21.48</v>
       </c>
       <c r="Z61" s="7" t="n">
-        <v>-17.35</v>
+        <v>-13.7</v>
       </c>
       <c r="AA61" s="7" t="n">
         <v>28.82</v>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>419.5</v>
+        <v>421</v>
       </c>
       <c r="C62" s="4" t="n">
         <v>1</v>
@@ -6154,22 +6154,22 @@
         <v>362.75</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>416</v>
+        <v>416.5</v>
       </c>
       <c r="H62" s="5" t="n">
         <v>-0.31</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0.0461</v>
+        <v>0.0499</v>
       </c>
       <c r="J62" s="5" t="n">
         <v>423.75</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>74.54000000000001</v>
+        <v>75.08</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>396.75</v>
@@ -6186,41 +6186,41 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P62" s="5" t="n">
         <v>12.5</v>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>410.75</v>
+        <v>411</v>
       </c>
       <c r="R62" s="5" t="n">
-        <v>415.75</v>
+        <v>416</v>
       </c>
       <c r="S62" s="5" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="T62" s="5" t="n">
         <v>11.75</v>
       </c>
       <c r="U62" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0282</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>0.0199</v>
+        <v>0.0198</v>
       </c>
       <c r="W62" s="5" t="n">
         <v>42.62</v>
       </c>
       <c r="X62" s="5" t="n">
-        <v>63.78</v>
+        <v>63.9</v>
       </c>
       <c r="Y62" s="5" t="n">
         <v>379.25</v>
       </c>
       <c r="Z62" s="5" t="n">
-        <v>-12.59</v>
+        <v>-8.15</v>
       </c>
       <c r="AA62" s="5" t="n">
         <v>33.59</v>
@@ -6230,225 +6230,225 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>ULUSE</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>30.2</v>
+        <v>298</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.1429</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1.02</v>
+        <v>-22.25</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>30</v>
+        <v>309</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.74</v>
+        <v>16.25</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>34.06</v>
+        <v>319</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.01</v>
+        <v>-0.13</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>-0.1272</v>
+        <v>0.0276</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>35.06</v>
+        <v>335</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>48.95</v>
+        <v>53.28</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>31.3</v>
+        <v>292</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.52</v>
+        <v>-5.25</v>
       </c>
       <c r="Q63" s="7" t="n">
-        <v>31.38</v>
+        <v>288</v>
       </c>
       <c r="R63" s="7" t="n">
-        <v>34.24</v>
+        <v>320.25</v>
       </c>
       <c r="S63" s="7" t="n">
-        <v>-2.96</v>
+        <v>0.75</v>
       </c>
       <c r="T63" s="7" t="n">
-        <v>1.72</v>
+        <v>17</v>
       </c>
       <c r="U63" s="8" t="n">
-        <v>0.0571</v>
+        <v>0.0573</v>
       </c>
       <c r="V63" s="8" t="n">
-        <v>0.0592</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="W63" s="7" t="n">
-        <v>26.06</v>
+        <v>13.19</v>
       </c>
       <c r="X63" s="7" t="n">
-        <v>68.06999999999999</v>
+        <v>39.15</v>
       </c>
       <c r="Y63" s="7" t="n">
-        <v>34.4</v>
+        <v>303.5</v>
       </c>
       <c r="Z63" s="7" t="n">
-        <v>-79.41</v>
+        <v>-46.54</v>
       </c>
       <c r="AA63" s="7" t="n">
-        <v>26.45</v>
+        <v>23.82</v>
       </c>
       <c r="AB63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>241.2</v>
+        <v>30.26</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.3571</v>
+        <v>0.4286</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>19</v>
+        <v>1.02</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>227.9</v>
+        <v>30</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>13.9</v>
+        <v>-0.76</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>269.6</v>
+        <v>34.06</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>-0.0958</v>
+        <v>-0.1254</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>280</v>
+        <v>35.06</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>53.65</v>
+        <v>49.15</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>238.7</v>
+        <v>31.3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="P64" s="5" t="n">
-        <v>6.5</v>
+        <v>0.52</v>
       </c>
       <c r="Q64" s="5" t="n">
-        <v>248.5</v>
+        <v>31.4</v>
       </c>
       <c r="R64" s="5" t="n">
-        <v>267.9</v>
+        <v>34.24</v>
       </c>
       <c r="S64" s="5" t="n">
-        <v>-13.6</v>
+        <v>-2.9</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>15.8</v>
+        <v>1.72</v>
       </c>
       <c r="U64" s="4" t="n">
-        <v>0.06570000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.0591</v>
       </c>
       <c r="W64" s="5" t="n">
-        <v>27.94</v>
+        <v>26.06</v>
       </c>
       <c r="X64" s="5" t="n">
-        <v>73.76000000000001</v>
+        <v>68.02</v>
       </c>
       <c r="Y64" s="5" t="n">
-        <v>263.5</v>
+        <v>34.4</v>
       </c>
       <c r="Z64" s="5" t="n">
-        <v>-54.27</v>
+        <v>-78.43000000000001</v>
       </c>
       <c r="AA64" s="5" t="n">
-        <v>34.23</v>
+        <v>26.45</v>
       </c>
       <c r="AB64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>ULUSE</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>294.25</v>
+        <v>241.6</v>
       </c>
       <c r="C65" s="8" t="n">
-        <v>0.1429</v>
+        <v>0.3571</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-22.25</v>
+        <v>19</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>309</v>
+        <v>227.9</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>17.5</v>
+        <v>13.8</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>318.5</v>
+        <v>269.6</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.0147</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>51.87</v>
+        <v>53.81</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>292</v>
+        <v>238.7</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -6462,85 +6462,85 @@
       </c>
       <c r="O65" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P65" s="7" t="n">
-        <v>-5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q65" s="7" t="n">
-        <v>287</v>
+        <v>248.6</v>
       </c>
       <c r="R65" s="7" t="n">
-        <v>320</v>
+        <v>267.9</v>
       </c>
       <c r="S65" s="7" t="n">
-        <v>-3</v>
+        <v>-13.2</v>
       </c>
       <c r="T65" s="7" t="n">
-        <v>17</v>
+        <v>15.8</v>
       </c>
       <c r="U65" s="8" t="n">
-        <v>0.058</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="V65" s="8" t="n">
-        <v>0.0529</v>
+        <v>0.0733</v>
       </c>
       <c r="W65" s="7" t="n">
-        <v>13.19</v>
+        <v>27.94</v>
       </c>
       <c r="X65" s="7" t="n">
-        <v>39.02</v>
+        <v>73.62</v>
       </c>
       <c r="Y65" s="7" t="n">
-        <v>303.5</v>
+        <v>263.5</v>
       </c>
       <c r="Z65" s="7" t="n">
-        <v>-51.26</v>
+        <v>-53.71</v>
       </c>
       <c r="AA65" s="7" t="n">
-        <v>23.82</v>
+        <v>34.23</v>
       </c>
       <c r="AB65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>DAGI</t>
+          <t>ETYAT</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>9.74</v>
+        <v>13.42</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>0.08</v>
+        <v>-0.38</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>8.58</v>
+        <v>12.7</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.67</v>
+        <v>0.18</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>9.890000000000001</v>
+        <v>13.94</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.0587</v>
+        <v>0.0198</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>10.35</v>
+        <v>14.18</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>59.56</v>
+        <v>56.09</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>9.35</v>
+        <v>13.29</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -6558,40 +6558,40 @@
         </is>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="Q66" s="5" t="n">
-        <v>9.5</v>
+        <v>13.31</v>
       </c>
       <c r="R66" s="5" t="n">
-        <v>10.3</v>
+        <v>14.65</v>
       </c>
       <c r="S66" s="5" t="n">
-        <v>0.04</v>
+        <v>0.29</v>
       </c>
       <c r="T66" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>0.0572</v>
+        <v>0.0551</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>0.0518</v>
+        <v>0.057</v>
       </c>
       <c r="W66" s="5" t="n">
-        <v>31.46</v>
+        <v>24.93</v>
       </c>
       <c r="X66" s="5" t="n">
-        <v>74.62</v>
+        <v>40.54</v>
       </c>
       <c r="Y66" s="5" t="n">
-        <v>8.529999999999999</v>
+        <v>11.46</v>
       </c>
       <c r="Z66" s="5" t="n">
-        <v>-13.57</v>
+        <v>-18.36</v>
       </c>
       <c r="AA66" s="5" t="n">
-        <v>26.26</v>
+        <v>14.97</v>
       </c>
       <c r="AB66" s="2" t="inlineStr"/>
     </row>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>227.8</v>
+        <v>228.1</v>
       </c>
       <c r="C67" s="8" t="n">
         <v>0.7857</v>
@@ -6614,22 +6614,22 @@
         <v>226.7</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>228.6</v>
+        <v>228.7</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0.04</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0454</v>
       </c>
       <c r="J67" s="7" t="n">
         <v>232.6</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>55.48</v>
+        <v>55.82</v>
       </c>
       <c r="L67" s="7" t="n">
         <v>219.9</v>
@@ -6646,20 +6646,20 @@
       </c>
       <c r="O67" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P67" s="7" t="n">
         <v>-1.2</v>
       </c>
       <c r="Q67" s="7" t="n">
-        <v>229.4</v>
+        <v>229.5</v>
       </c>
       <c r="R67" s="7" t="n">
         <v>236.6</v>
       </c>
       <c r="S67" s="7" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="T67" s="7" t="n">
         <v>7.6</v>
@@ -6674,13 +6674,13 @@
         <v>18.89</v>
       </c>
       <c r="X67" s="7" t="n">
-        <v>48.8</v>
+        <v>48.85</v>
       </c>
       <c r="Y67" s="7" t="n">
         <v>210.1</v>
       </c>
       <c r="Z67" s="7" t="n">
-        <v>-20.51</v>
+        <v>-19.23</v>
       </c>
       <c r="AA67" s="7" t="n">
         <v>31.37</v>
@@ -6690,45 +6690,45 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ETYAT</t>
+          <t>FONET</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>13.3</v>
+        <v>5.19</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.2143</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>12.7</v>
+        <v>5.33</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>13.93</v>
+        <v>5.48</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.21</v>
+        <v>-0.08</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0.0106</v>
+        <v>-0.0299</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>14.18</v>
+        <v>5.54</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>54.53</v>
+        <v>49.55</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>13.29</v>
+        <v>5.16</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -6738,136 +6738,136 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="Q68" s="5" t="n">
-        <v>13.27</v>
+        <v>5.14</v>
       </c>
       <c r="R68" s="5" t="n">
-        <v>14.64</v>
+        <v>5.68</v>
       </c>
       <c r="S68" s="5" t="n">
-        <v>0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="U68" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>0.0575</v>
+        <v>0.048</v>
       </c>
       <c r="W68" s="5" t="n">
-        <v>24.93</v>
+        <v>13.1</v>
       </c>
       <c r="X68" s="5" t="n">
-        <v>40.96</v>
+        <v>57.76</v>
       </c>
       <c r="Y68" s="5" t="n">
-        <v>11.46</v>
+        <v>5.36</v>
       </c>
       <c r="Z68" s="5" t="n">
-        <v>-23.05</v>
+        <v>-50.72</v>
       </c>
       <c r="AA68" s="5" t="n">
-        <v>14.97</v>
+        <v>15.62</v>
       </c>
       <c r="AB68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>FONET</t>
+          <t>DAGI</t>
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>5.19</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C69" s="8" t="n">
-        <v>0.2143</v>
+        <v>1</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>5.33</v>
+        <v>8.58</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>5.48</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>-0.08</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>-0.0299</v>
+        <v>0.0478</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>5.54</v>
+        <v>10.35</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>49.55</v>
+        <v>58.4</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>5.16</v>
+        <v>9.35</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P69" s="7" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="Q69" s="7" t="n">
-        <v>5.14</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="R69" s="7" t="n">
-        <v>5.68</v>
+        <v>10.3</v>
       </c>
       <c r="S69" s="7" t="n">
-        <v>-0.14</v>
+        <v>-0.06</v>
       </c>
       <c r="T69" s="7" t="n">
-        <v>0.26</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U69" s="8" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V69" s="8" t="n">
-        <v>0.048</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="W69" s="7" t="n">
-        <v>13.1</v>
+        <v>31.46</v>
       </c>
       <c r="X69" s="7" t="n">
-        <v>57.67</v>
+        <v>74.75</v>
       </c>
       <c r="Y69" s="7" t="n">
-        <v>5.36</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="Z69" s="7" t="n">
-        <v>-50.72</v>
+        <v>-20.71</v>
       </c>
       <c r="AA69" s="7" t="n">
-        <v>15.62</v>
+        <v>26.26</v>
       </c>
       <c r="AB69" s="6" t="inlineStr"/>
     </row>
@@ -6950,7 +6950,7 @@
         <v>14.63</v>
       </c>
       <c r="X70" s="5" t="n">
-        <v>65.43000000000001</v>
+        <v>65.61</v>
       </c>
       <c r="Y70" s="5" t="n">
         <v>5.11</v>
@@ -6970,7 +6970,7 @@
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="C71" s="8" t="n">
         <v>0.3571</v>
@@ -6982,7 +6982,7 @@
         <v>21.68</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>24.36</v>
@@ -6991,25 +6991,25 @@
         <v>-0.12</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>-0.1107</v>
+        <v>-0.1148</v>
       </c>
       <c r="J71" s="7" t="n">
         <v>24.98</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>49.77</v>
+        <v>49.21</v>
       </c>
       <c r="L71" s="7" t="n">
         <v>22.3</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
@@ -7021,34 +7021,34 @@
         <v>0.14</v>
       </c>
       <c r="Q71" s="7" t="n">
-        <v>21.4</v>
+        <v>21.36</v>
       </c>
       <c r="R71" s="7" t="n">
-        <v>24.22</v>
+        <v>24.2</v>
       </c>
       <c r="S71" s="7" t="n">
-        <v>-2.12</v>
+        <v>-2.22</v>
       </c>
       <c r="T71" s="7" t="n">
         <v>1.24</v>
       </c>
       <c r="U71" s="8" t="n">
-        <v>0.0568</v>
+        <v>0.057</v>
       </c>
       <c r="V71" s="8" t="n">
-        <v>0.0588</v>
+        <v>0.0591</v>
       </c>
       <c r="W71" s="7" t="n">
         <v>21.1</v>
       </c>
       <c r="X71" s="7" t="n">
-        <v>67.73999999999999</v>
+        <v>67.69</v>
       </c>
       <c r="Y71" s="7" t="n">
         <v>24.24</v>
       </c>
       <c r="Z71" s="7" t="n">
-        <v>-73.20999999999999</v>
+        <v>-75.45</v>
       </c>
       <c r="AA71" s="7" t="n">
         <v>19.26</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>28.98</v>
+        <v>28.86</v>
       </c>
       <c r="C72" s="4" t="n">
         <v>0.07139999999999999</v>
@@ -7074,7 +7074,7 @@
         <v>30.94</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-3.08</v>
+        <v>-3.04</v>
       </c>
       <c r="G72" s="5" t="n">
         <v>34.54</v>
@@ -7083,13 +7083,13 @@
         <v>-0.02</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>-0.0585</v>
+        <v>-0.0624</v>
       </c>
       <c r="J72" s="5" t="n">
         <v>36.36</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>44.85</v>
+        <v>44.3</v>
       </c>
       <c r="L72" s="5" t="n">
         <v>31.12</v>
@@ -7110,25 +7110,25 @@
         </is>
       </c>
       <c r="P72" s="5" t="n">
-        <v>-0.58</v>
+        <v>-0.6</v>
       </c>
       <c r="Q72" s="5" t="n">
-        <v>29.1</v>
+        <v>29.06</v>
       </c>
       <c r="R72" s="5" t="n">
-        <v>34.06</v>
+        <v>34.04</v>
       </c>
       <c r="S72" s="5" t="n">
-        <v>-1.52</v>
+        <v>-1.64</v>
       </c>
       <c r="T72" s="5" t="n">
         <v>2.18</v>
       </c>
       <c r="U72" s="4" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="V72" s="4" t="n">
-        <v>0.0653</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="W72" s="5" t="n">
         <v>14.09</v>
@@ -7140,7 +7140,7 @@
         <v>30.96</v>
       </c>
       <c r="Z72" s="5" t="n">
-        <v>-71.45999999999999</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="AA72" s="5" t="n">
         <v>16.62</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>142</v>
+        <v>141.7</v>
       </c>
       <c r="C73" s="8" t="n">
         <v>0.5</v>
@@ -7169,19 +7169,19 @@
         <v>2.3</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>153.4</v>
+        <v>153.3</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0.22</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.0121</v>
+        <v>0.01</v>
       </c>
       <c r="J73" s="7" t="n">
         <v>147.2</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>53.01</v>
+        <v>52.71</v>
       </c>
       <c r="L73" s="7" t="n">
         <v>132.1</v>
@@ -7211,13 +7211,13 @@
         <v>152.6</v>
       </c>
       <c r="S73" s="7" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="T73" s="7" t="n">
         <v>6.8</v>
       </c>
       <c r="U73" s="8" t="n">
-        <v>0.0479</v>
+        <v>0.048</v>
       </c>
       <c r="V73" s="8" t="n">
         <v>0.0418</v>
@@ -7226,13 +7226,13 @@
         <v>13.46</v>
       </c>
       <c r="X73" s="7" t="n">
-        <v>56.9</v>
+        <v>56.87</v>
       </c>
       <c r="Y73" s="7" t="n">
         <v>126.8</v>
       </c>
       <c r="Z73" s="7" t="n">
-        <v>-39.1</v>
+        <v>-41.35</v>
       </c>
       <c r="AA73" s="7" t="n">
         <v>23.15</v>
@@ -7318,7 +7318,7 @@
         <v>25.08</v>
       </c>
       <c r="X74" s="5" t="n">
-        <v>45.33</v>
+        <v>45.28</v>
       </c>
       <c r="Y74" s="5" t="n">
         <v>45.14</v>
@@ -7334,217 +7334,217 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>ORZAX</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>114.8</v>
+        <v>132.3</v>
       </c>
       <c r="C75" s="8" t="n">
-        <v>0.9286</v>
-      </c>
-      <c r="D75" s="6" t="inlineStr"/>
-      <c r="E75" s="6" t="inlineStr"/>
+        <v>0.1429</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>162.8</v>
+      </c>
       <c r="F75" s="7" t="n">
-        <v>24.3</v>
+        <v>-4.6</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>118.8</v>
+        <v>148</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>0.18</v>
+        <v>-0.28</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.1255</v>
+        <v>-0.0357</v>
       </c>
       <c r="J75" s="7" t="n">
-        <v>122.3</v>
+        <v>155.2</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>71.13</v>
+        <v>38.75</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>100.3</v>
+        <v>138.3</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Güçlü sat</t>
         </is>
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="P75" s="6" t="inlineStr"/>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="n">
+        <v>-7.9</v>
+      </c>
       <c r="Q75" s="7" t="n">
-        <v>117.6</v>
+        <v>134.7</v>
       </c>
       <c r="R75" s="7" t="n">
-        <v>118.6</v>
+        <v>154.7</v>
       </c>
       <c r="S75" s="7" t="n">
-        <v>10.3</v>
+        <v>-7.7</v>
       </c>
       <c r="T75" s="7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U75" s="8" t="n">
-        <v>0.0756</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="V75" s="8" t="n">
-        <v>0.0668</v>
-      </c>
-      <c r="W75" s="6" t="inlineStr"/>
+        <v>0.0594</v>
+      </c>
+      <c r="W75" s="7" t="n">
+        <v>21.6</v>
+      </c>
       <c r="X75" s="7" t="n">
-        <v>59.45</v>
+        <v>57.45</v>
       </c>
       <c r="Y75" s="7" t="n">
-        <v>95.90000000000001</v>
+        <v>141.8</v>
       </c>
       <c r="Z75" s="7" t="n">
-        <v>-26.88</v>
+        <v>-78.16</v>
       </c>
       <c r="AA75" s="7" t="n">
-        <v>34.54</v>
+        <v>15.21</v>
       </c>
       <c r="AB75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ORZAX</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>132.3</v>
+        <v>112.3</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="D76" s="5" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>162.8</v>
-      </c>
+        <v>0.9286</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="5" t="n">
-        <v>-4.6</v>
+        <v>22.9</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>148</v>
+        <v>118.3</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>-0.28</v>
+        <v>0.17</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>-0.0357</v>
+        <v>0.101</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>155.2</v>
+        <v>122.3</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>38.75</v>
+        <v>68.36</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>138.3</v>
+        <v>100.3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Güçlü sat</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="P76" s="5" t="n">
-        <v>-7.9</v>
-      </c>
+      <c r="P76" s="2" t="inlineStr"/>
       <c r="Q76" s="5" t="n">
-        <v>134.7</v>
+        <v>116.9</v>
       </c>
       <c r="R76" s="5" t="n">
-        <v>154.7</v>
+        <v>118.8</v>
       </c>
       <c r="S76" s="5" t="n">
-        <v>-7.7</v>
+        <v>7.8</v>
       </c>
       <c r="T76" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U76" s="4" t="n">
-        <v>0.06179999999999999</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>0.0594</v>
-      </c>
-      <c r="W76" s="5" t="n">
-        <v>21.6</v>
-      </c>
+        <v>0.0696</v>
+      </c>
+      <c r="W76" s="2" t="inlineStr"/>
       <c r="X76" s="5" t="n">
-        <v>57.5</v>
+        <v>58.98</v>
       </c>
       <c r="Y76" s="5" t="n">
-        <v>141.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Z76" s="5" t="n">
-        <v>-78.16</v>
+        <v>-35.84</v>
       </c>
       <c r="AA76" s="5" t="n">
-        <v>15.21</v>
+        <v>33.97</v>
       </c>
       <c r="AB76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>EBEBK</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>90.15000000000001</v>
+        <v>191.4</v>
       </c>
       <c r="C77" s="8" t="n">
-        <v>0.7857</v>
+        <v>1</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>8</v>
+        <v>19.4</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>82</v>
+        <v>151.5</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>7.35</v>
+        <v>31.3</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>92.3</v>
+        <v>187.1</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>0.0446</v>
+        <v>0.2068</v>
       </c>
       <c r="J77" s="7" t="n">
-        <v>92.15000000000001</v>
+        <v>191.4</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>65.97</v>
+        <v>69.08</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>84.8</v>
+        <v>166.3</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -7562,81 +7562,81 @@
         </is>
       </c>
       <c r="P77" s="7" t="n">
-        <v>2.75</v>
+        <v>8.1</v>
       </c>
       <c r="Q77" s="7" t="n">
-        <v>91</v>
+        <v>182.3</v>
       </c>
       <c r="R77" s="7" t="n">
-        <v>91.25</v>
+        <v>184.2</v>
       </c>
       <c r="S77" s="7" t="n">
-        <v>5.15</v>
+        <v>31.3</v>
       </c>
       <c r="T77" s="7" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="U77" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0495</v>
       </c>
       <c r="V77" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.0489</v>
       </c>
       <c r="W77" s="7" t="n">
-        <v>39.75</v>
+        <v>33.44</v>
       </c>
       <c r="X77" s="7" t="n">
-        <v>64.34999999999999</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="Y77" s="7" t="n">
-        <v>82.5</v>
+        <v>164.4</v>
       </c>
       <c r="Z77" s="7" t="n">
-        <v>-18.96</v>
+        <v>0</v>
       </c>
       <c r="AA77" s="7" t="n">
-        <v>30.57</v>
+        <v>32.58</v>
       </c>
       <c r="AB77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>EBEBK</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>191.4</v>
+        <v>89.25</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>1</v>
+        <v>0.7857</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>19.4</v>
+        <v>8</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>151.5</v>
+        <v>81.95</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>31.3</v>
+        <v>7.6</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>187.1</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0.2068</v>
+        <v>0.0342</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>191.4</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>69.08</v>
+        <v>64.44</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>166.3</v>
+        <v>84.8</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -7654,40 +7654,40 @@
         </is>
       </c>
       <c r="P78" s="5" t="n">
-        <v>8.1</v>
+        <v>2.65</v>
       </c>
       <c r="Q78" s="5" t="n">
-        <v>182.3</v>
+        <v>90.7</v>
       </c>
       <c r="R78" s="5" t="n">
-        <v>184.2</v>
+        <v>91.2</v>
       </c>
       <c r="S78" s="5" t="n">
-        <v>31.3</v>
+        <v>4.25</v>
       </c>
       <c r="T78" s="5" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="U78" s="4" t="n">
-        <v>0.0495</v>
+        <v>0.0337</v>
       </c>
       <c r="V78" s="4" t="n">
-        <v>0.0489</v>
+        <v>0.0337</v>
       </c>
       <c r="W78" s="5" t="n">
-        <v>33.44</v>
+        <v>39.75</v>
       </c>
       <c r="X78" s="5" t="n">
-        <v>72.81</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="Y78" s="5" t="n">
-        <v>164.4</v>
+        <v>82.5</v>
       </c>
       <c r="Z78" s="5" t="n">
-        <v>0</v>
+        <v>-27.49</v>
       </c>
       <c r="AA78" s="5" t="n">
-        <v>32.58</v>
+        <v>30.57</v>
       </c>
       <c r="AB78" s="2" t="inlineStr"/>
     </row>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>41.68</v>
+        <v>41.64</v>
       </c>
       <c r="C79" s="8" t="n">
         <v>0.1429</v>
@@ -7710,7 +7710,7 @@
         <v>40.82</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>46.48</v>
@@ -7719,20 +7719,20 @@
         <v>0.28</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.0253</v>
+        <v>-0.0262</v>
       </c>
       <c r="J79" s="7" t="n">
         <v>49.5</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>49.58</v>
+        <v>49.44</v>
       </c>
       <c r="L79" s="7" t="n">
         <v>42.8</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="N79" s="6" t="inlineStr">
@@ -7755,28 +7755,28 @@
         <v>45.9</v>
       </c>
       <c r="S79" s="7" t="n">
-        <v>-2.7</v>
+        <v>-2.74</v>
       </c>
       <c r="T79" s="7" t="n">
         <v>1.86</v>
       </c>
       <c r="U79" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.0445</v>
       </c>
       <c r="V79" s="8" t="n">
-        <v>0.0599</v>
+        <v>0.06</v>
       </c>
       <c r="W79" s="7" t="n">
         <v>19.83</v>
       </c>
       <c r="X79" s="7" t="n">
-        <v>57.94</v>
+        <v>57.88</v>
       </c>
       <c r="Y79" s="7" t="n">
         <v>47.12</v>
       </c>
       <c r="Z79" s="7" t="n">
-        <v>-90.93000000000001</v>
+        <v>-91.40000000000001</v>
       </c>
       <c r="AA79" s="7" t="n">
         <v>25.02</v>
@@ -7786,45 +7786,45 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>81.45</v>
+        <v>14.74</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0.1429</v>
+        <v>0.4286</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>0.85</v>
+        <v>0.31</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>78.8</v>
+        <v>13.93</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>5.6</v>
+        <v>0.05</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>87.65000000000001</v>
+        <v>15.04</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>-0.31</v>
+        <v>-0.1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0.0018</v>
+        <v>-0.0173</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>92</v>
+        <v>15.28</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>55.47</v>
+        <v>57.14</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>81.5</v>
+        <v>14.81</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -7838,40 +7838,40 @@
         </is>
       </c>
       <c r="P80" s="5" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="Q80" s="5" t="n">
-        <v>81.55</v>
+        <v>14.73</v>
       </c>
       <c r="R80" s="5" t="n">
-        <v>86.65000000000001</v>
+        <v>15.32</v>
       </c>
       <c r="S80" s="5" t="n">
-        <v>-1.15</v>
+        <v>-0.21</v>
       </c>
       <c r="T80" s="5" t="n">
-        <v>4.1</v>
+        <v>0.35</v>
       </c>
       <c r="U80" s="4" t="n">
-        <v>0.0503</v>
+        <v>0.0236</v>
       </c>
       <c r="V80" s="4" t="n">
-        <v>0.0509</v>
+        <v>0.0209</v>
       </c>
       <c r="W80" s="5" t="n">
-        <v>18.34</v>
+        <v>23.84</v>
       </c>
       <c r="X80" s="5" t="n">
-        <v>60.52</v>
+        <v>52.92</v>
       </c>
       <c r="Y80" s="5" t="n">
-        <v>83.90000000000001</v>
+        <v>14.15</v>
       </c>
       <c r="Z80" s="5" t="n">
-        <v>-51.97</v>
+        <v>-46.96</v>
       </c>
       <c r="AA80" s="5" t="n">
-        <v>30.24</v>
+        <v>27.49</v>
       </c>
       <c r="AB80" s="2" t="inlineStr"/>
     </row>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>45.96</v>
+        <v>46.02</v>
       </c>
       <c r="C81" s="8" t="n">
         <v>1</v>
@@ -7894,25 +7894,25 @@
         <v>39.22</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>11.84</v>
+        <v>11.82</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>44.42</v>
+        <v>44.44</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>0.2322</v>
+        <v>0.2338</v>
       </c>
       <c r="J81" s="7" t="n">
         <v>48.1</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>67.79000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>40.28</v>
+        <v>40.3</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -7933,34 +7933,34 @@
         <v>0.7</v>
       </c>
       <c r="Q81" s="7" t="n">
-        <v>44.3</v>
+        <v>44.32</v>
       </c>
       <c r="R81" s="7" t="n">
         <v>45.38</v>
       </c>
       <c r="S81" s="7" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
       <c r="T81" s="7" t="n">
         <v>2.74</v>
       </c>
       <c r="U81" s="8" t="n">
-        <v>0.0594</v>
+        <v>0.0593</v>
       </c>
       <c r="V81" s="8" t="n">
-        <v>0.0582</v>
+        <v>0.0581</v>
       </c>
       <c r="W81" s="7" t="n">
         <v>20.37</v>
       </c>
       <c r="X81" s="7" t="n">
-        <v>75.52</v>
+        <v>75.58</v>
       </c>
       <c r="Y81" s="7" t="n">
         <v>33.58</v>
       </c>
       <c r="Z81" s="7" t="n">
-        <v>-14.27</v>
+        <v>-13.87</v>
       </c>
       <c r="AA81" s="7" t="n">
         <v>38.61</v>
@@ -7970,317 +7970,317 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>41.56</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0.2857</v>
+        <v>0.1429</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>40.96</v>
+        <v>78.8</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>-0.52</v>
+        <v>5.5</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>44.68</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.31</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>-0.0397</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>45.1</v>
+        <v>92</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>48.94</v>
+        <v>55.28</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>42.4</v>
+        <v>81.5</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
       <c r="P82" s="5" t="n">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="Q82" s="5" t="n">
-        <v>41.22</v>
+        <v>81.5</v>
       </c>
       <c r="R82" s="5" t="n">
-        <v>44.86</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="S82" s="5" t="n">
-        <v>-2.64</v>
+        <v>-1.25</v>
       </c>
       <c r="T82" s="5" t="n">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
       <c r="U82" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.0504</v>
       </c>
       <c r="V82" s="4" t="n">
-        <v>0.0368</v>
+        <v>0.051</v>
       </c>
       <c r="W82" s="5" t="n">
-        <v>23.52</v>
+        <v>18.34</v>
       </c>
       <c r="X82" s="5" t="n">
-        <v>42.1</v>
+        <v>59.37</v>
       </c>
       <c r="Y82" s="5" t="n">
-        <v>44.52</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z82" s="5" t="n">
-        <v>-77.63</v>
+        <v>-52.46</v>
       </c>
       <c r="AA82" s="5" t="n">
-        <v>17.33</v>
+        <v>30.18</v>
       </c>
       <c r="AB82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>32.72</v>
+        <v>41.6</v>
       </c>
       <c r="C83" s="8" t="n">
-        <v>0.2143</v>
+        <v>0.2857</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.24</v>
+        <v>0.2</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>33.5</v>
+        <v>40.96</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>0.86</v>
+        <v>-0.52</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>35.26</v>
+        <v>44.68</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.0151</v>
+        <v>-0.0388</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>35.78</v>
+        <v>45.1</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>50.14</v>
+        <v>49.12</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>32.66</v>
+        <v>42.4</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P83" s="7" t="n">
-        <v>-0.14</v>
+        <v>0.34</v>
       </c>
       <c r="Q83" s="7" t="n">
-        <v>33.1</v>
+        <v>41.24</v>
       </c>
       <c r="R83" s="7" t="n">
-        <v>35.92</v>
+        <v>44.86</v>
       </c>
       <c r="S83" s="7" t="n">
-        <v>-1.38</v>
+        <v>-2.6</v>
       </c>
       <c r="T83" s="7" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="U83" s="8" t="n">
-        <v>0.051</v>
+        <v>0.0346</v>
       </c>
       <c r="V83" s="8" t="n">
-        <v>0.0515</v>
+        <v>0.0367</v>
       </c>
       <c r="W83" s="7" t="n">
-        <v>14.83</v>
+        <v>23.52</v>
       </c>
       <c r="X83" s="7" t="n">
-        <v>55.12</v>
+        <v>41.95</v>
       </c>
       <c r="Y83" s="7" t="n">
-        <v>34.44</v>
+        <v>44.52</v>
       </c>
       <c r="Z83" s="7" t="n">
-        <v>-52.04</v>
+        <v>-76.75</v>
       </c>
       <c r="AA83" s="7" t="n">
-        <v>22.41</v>
+        <v>17.33</v>
       </c>
       <c r="AB83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ETILR</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>5.92</v>
+        <v>32.74</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.2143</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.24</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>5.8</v>
+        <v>33.5</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.08</v>
+        <v>0.86</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>6.85</v>
+        <v>35.26</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>-0.0706</v>
+        <v>-0.0144</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>6.91</v>
+        <v>35.78</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>49.25</v>
+        <v>50.22</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>6.25</v>
+        <v>32.66</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
       <c r="P84" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="Q84" s="5" t="n">
-        <v>5.88</v>
+        <v>33.1</v>
       </c>
       <c r="R84" s="5" t="n">
-        <v>6.72</v>
+        <v>35.94</v>
       </c>
       <c r="S84" s="5" t="n">
-        <v>-0.55</v>
+        <v>-1.36</v>
       </c>
       <c r="T84" s="5" t="n">
-        <v>0.38</v>
+        <v>1.66</v>
       </c>
       <c r="U84" s="4" t="n">
-        <v>0.06480000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="V84" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0515</v>
       </c>
       <c r="W84" s="5" t="n">
-        <v>18.59</v>
+        <v>14.83</v>
       </c>
       <c r="X84" s="5" t="n">
-        <v>37.55</v>
+        <v>55.02</v>
       </c>
       <c r="Y84" s="5" t="n">
-        <v>6.38</v>
+        <v>34.44</v>
       </c>
       <c r="Z84" s="5" t="n">
-        <v>-66.44</v>
+        <v>-51.7</v>
       </c>
       <c r="AA84" s="5" t="n">
-        <v>17.31</v>
+        <v>22.41</v>
       </c>
       <c r="AB84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>ETILR</t>
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>14.61</v>
+        <v>5.92</v>
       </c>
       <c r="C85" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0.31</v>
+        <v>-0.06</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>13.93</v>
+        <v>5.8</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>15.04</v>
+        <v>6.85</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.026</v>
+        <v>-0.0706</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>15.28</v>
+        <v>6.91</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>51.37</v>
+        <v>49.25</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>14.81</v>
+        <v>6.25</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -8289,141 +8289,141 @@
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="O85" s="6" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
       <c r="P85" s="7" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="Q85" s="7" t="n">
-        <v>14.69</v>
+        <v>5.88</v>
       </c>
       <c r="R85" s="7" t="n">
-        <v>15.31</v>
+        <v>6.72</v>
       </c>
       <c r="S85" s="7" t="n">
-        <v>-0.34</v>
+        <v>-0.55</v>
       </c>
       <c r="T85" s="7" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="U85" s="8" t="n">
-        <v>0.0238</v>
+        <v>0.06480000000000001</v>
       </c>
       <c r="V85" s="8" t="n">
-        <v>0.021</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="W85" s="7" t="n">
-        <v>23.88</v>
+        <v>18.59</v>
       </c>
       <c r="X85" s="7" t="n">
-        <v>53.29</v>
+        <v>37.55</v>
       </c>
       <c r="Y85" s="7" t="n">
-        <v>14.15</v>
+        <v>6.38</v>
       </c>
       <c r="Z85" s="7" t="n">
-        <v>-58.26</v>
+        <v>-66.44</v>
       </c>
       <c r="AA85" s="7" t="n">
-        <v>27.55</v>
+        <v>17.31</v>
       </c>
       <c r="AB85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>VANGD</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>90.15000000000001</v>
+        <v>3.71</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0.2857</v>
+        <v>0.3571</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>-4.2</v>
+        <v>0.1</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>91.65000000000001</v>
+        <v>3.46</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-3.4</v>
+        <v>0.14</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>97.7</v>
+        <v>4.01</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>-0.0301</v>
+        <v>-0.008</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>102.5</v>
+        <v>4.25</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>48.16</v>
+        <v>55.95</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>92.40000000000001</v>
+        <v>3.57</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
           <t>Nötr</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
       <c r="P86" s="5" t="n">
-        <v>-0.95</v>
+        <v>0.08</v>
       </c>
       <c r="Q86" s="5" t="n">
-        <v>88.5</v>
+        <v>3.72</v>
       </c>
       <c r="R86" s="5" t="n">
-        <v>99.2</v>
+        <v>4.01</v>
       </c>
       <c r="S86" s="5" t="n">
-        <v>-4.65</v>
+        <v>-0.25</v>
       </c>
       <c r="T86" s="5" t="n">
-        <v>4.5</v>
+        <v>0.22</v>
       </c>
       <c r="U86" s="4" t="n">
-        <v>0.0499</v>
+        <v>0.0592</v>
       </c>
       <c r="V86" s="4" t="n">
-        <v>0.042</v>
+        <v>0.0664</v>
       </c>
       <c r="W86" s="5" t="n">
-        <v>17.12</v>
+        <v>27.53</v>
       </c>
       <c r="X86" s="5" t="n">
-        <v>36.15</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="Y86" s="5" t="n">
-        <v>99.05</v>
+        <v>4.2</v>
       </c>
       <c r="Z86" s="5" t="n">
-        <v>-62.27</v>
+        <v>-49.54</v>
       </c>
       <c r="AA86" s="5" t="n">
-        <v>18.53</v>
+        <v>32.64</v>
       </c>
       <c r="AB86" s="2" t="inlineStr"/>
     </row>
@@ -8506,7 +8506,7 @@
         <v>16.32</v>
       </c>
       <c r="X87" s="7" t="n">
-        <v>70.47</v>
+        <v>70.3</v>
       </c>
       <c r="Y87" s="7" t="n">
         <v>98.8</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>14.54</v>
+        <v>14.53</v>
       </c>
       <c r="C88" s="4" t="n">
         <v>0.8571</v>
@@ -8544,19 +8544,19 @@
         <v>15.02</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0048</v>
       </c>
       <c r="J88" s="5" t="n">
         <v>15.77</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>51.53</v>
+        <v>51.37</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>14.55</v>
+        <v>14.54</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>15.74</v>
       </c>
       <c r="S88" s="5" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="T88" s="5" t="n">
         <v>0.62</v>
@@ -8598,13 +8598,13 @@
         <v>26.14</v>
       </c>
       <c r="X88" s="5" t="n">
-        <v>60.14</v>
+        <v>60.06</v>
       </c>
       <c r="Y88" s="5" t="n">
         <v>13.64</v>
       </c>
       <c r="Z88" s="5" t="n">
-        <v>-55.41</v>
+        <v>-55.86</v>
       </c>
       <c r="AA88" s="5" t="n">
         <v>26.99</v>
@@ -8618,37 +8618,37 @@
         </is>
       </c>
       <c r="B89" s="7" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="C89" s="8" t="n">
         <v>0.4286</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>20.12</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>22</v>
+        <v>22.04</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.0037</v>
       </c>
       <c r="J89" s="7" t="n">
         <v>22.48</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>62.04</v>
+        <v>63.03</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>20.2</v>
+        <v>20.22</v>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
@@ -8662,94 +8662,94 @@
       </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P89" s="7" t="n">
         <v>0.4</v>
       </c>
       <c r="Q89" s="7" t="n">
-        <v>21.16</v>
+        <v>21.22</v>
       </c>
       <c r="R89" s="7" t="n">
-        <v>22.4</v>
+        <v>22.42</v>
       </c>
       <c r="S89" s="7" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="T89" s="7" t="n">
         <v>1.12</v>
       </c>
       <c r="U89" s="8" t="n">
-        <v>0.0516</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="V89" s="8" t="n">
-        <v>0.0581</v>
+        <v>0.0579</v>
       </c>
       <c r="W89" s="7" t="n">
-        <v>28.61</v>
+        <v>28.67</v>
       </c>
       <c r="X89" s="7" t="n">
-        <v>68.23</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Y89" s="7" t="n">
-        <v>21.88</v>
+        <v>18.82</v>
       </c>
       <c r="Z89" s="7" t="n">
-        <v>-22.4</v>
+        <v>-16.94</v>
       </c>
       <c r="AA89" s="7" t="n">
-        <v>25.56</v>
+        <v>25.94</v>
       </c>
       <c r="AB89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>AYES</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>3.66</v>
+        <v>29.8</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>0.3571</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>0.1</v>
+        <v>-3.78</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3.46</v>
+        <v>32.6</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.15</v>
+        <v>-0.42</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>4</v>
+        <v>34.04</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>-0.09</v>
+        <v>0.29</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>-0.0214</v>
+        <v>-0.0455</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>4.25</v>
+        <v>33</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>54.44</v>
+        <v>46.16</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>3.57</v>
+        <v>29.46</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -8758,90 +8758,90 @@
         </is>
       </c>
       <c r="P90" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.22</v>
       </c>
       <c r="Q90" s="5" t="n">
-        <v>3.71</v>
+        <v>27.24</v>
       </c>
       <c r="R90" s="5" t="n">
-        <v>4</v>
+        <v>32.62</v>
       </c>
       <c r="S90" s="5" t="n">
-        <v>-0.3</v>
+        <v>-1.22</v>
       </c>
       <c r="T90" s="5" t="n">
-        <v>0.22</v>
+        <v>1.16</v>
       </c>
       <c r="U90" s="4" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.0388</v>
       </c>
       <c r="V90" s="4" t="n">
-        <v>0.06709999999999999</v>
+        <v>0.0311</v>
       </c>
       <c r="W90" s="5" t="n">
-        <v>27.53</v>
+        <v>19.29</v>
       </c>
       <c r="X90" s="5" t="n">
-        <v>68.98999999999999</v>
+        <v>61.75</v>
       </c>
       <c r="Y90" s="5" t="n">
-        <v>4.2</v>
+        <v>29.84</v>
       </c>
       <c r="Z90" s="5" t="n">
-        <v>-54.13</v>
+        <v>-42.19</v>
       </c>
       <c r="AA90" s="5" t="n">
-        <v>32.75</v>
+        <v>28.26</v>
       </c>
       <c r="AB90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>KRDMD</t>
+          <t>VANGD</t>
         </is>
       </c>
       <c r="B91" s="7" t="n">
-        <v>41.58</v>
+        <v>88.45</v>
       </c>
       <c r="C91" s="8" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.2857</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>0.7</v>
+        <v>-4.2</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>40.36</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>1.1</v>
+        <v>-2.5</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>45.26</v>
+        <v>97.75</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>-0.0147</v>
+        <v>-0.0484</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>45.1</v>
+        <v>102.5</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>52.2</v>
+        <v>44.52</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>41.6</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="O91" s="6" t="inlineStr">
@@ -8850,90 +8850,90 @@
         </is>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0.48</v>
+        <v>-1.1</v>
       </c>
       <c r="Q91" s="7" t="n">
-        <v>41.76</v>
+        <v>88</v>
       </c>
       <c r="R91" s="7" t="n">
-        <v>44.44</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S91" s="7" t="n">
-        <v>-0.58</v>
+        <v>-6.35</v>
       </c>
       <c r="T91" s="7" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="U91" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="V91" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0431</v>
       </c>
       <c r="W91" s="7" t="n">
-        <v>12.68</v>
+        <v>17.24</v>
       </c>
       <c r="X91" s="7" t="n">
-        <v>42.32</v>
+        <v>36.65</v>
       </c>
       <c r="Y91" s="7" t="n">
-        <v>43.8</v>
+        <v>99.05</v>
       </c>
       <c r="Z91" s="7" t="n">
-        <v>-67.43000000000001</v>
+        <v>-77.73</v>
       </c>
       <c r="AA91" s="7" t="n">
-        <v>20.42</v>
+        <v>19.04</v>
       </c>
       <c r="AB91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>ECOGR</t>
+          <t>KRDMD</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>33.98</v>
+        <v>41.7</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0.2857</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>-4.52</v>
+        <v>0.7</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>39</v>
+        <v>40.36</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-4.76</v>
+        <v>1.06</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>44.54</v>
+        <v>45.28</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>-0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>-0.2316</v>
+        <v>-0.0118</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>45.72</v>
+        <v>45.1</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>39.73</v>
+        <v>52.73</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>39.38</v>
+        <v>41.6</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Güçlü sat</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Güçlü sat</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -8942,132 +8942,132 @@
         </is>
       </c>
       <c r="P92" s="5" t="n">
-        <v>-1.44</v>
+        <v>0.48</v>
       </c>
       <c r="Q92" s="5" t="n">
-        <v>34.36</v>
+        <v>41.8</v>
       </c>
       <c r="R92" s="5" t="n">
-        <v>42.68</v>
+        <v>44.44</v>
       </c>
       <c r="S92" s="5" t="n">
-        <v>-10.22</v>
+        <v>-0.46</v>
       </c>
       <c r="T92" s="5" t="n">
-        <v>2.56</v>
+        <v>1.6</v>
       </c>
       <c r="U92" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0381</v>
       </c>
       <c r="V92" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0385</v>
       </c>
       <c r="W92" s="5" t="n">
-        <v>17.21</v>
+        <v>12.68</v>
       </c>
       <c r="X92" s="5" t="n">
-        <v>42.32</v>
+        <v>42.26</v>
       </c>
       <c r="Y92" s="5" t="n">
-        <v>41.5</v>
+        <v>43.8</v>
       </c>
       <c r="Z92" s="5" t="n">
-        <v>-83.98</v>
+        <v>-65.13</v>
       </c>
       <c r="AA92" s="5" t="n">
-        <v>22.31</v>
+        <v>20.42</v>
       </c>
       <c r="AB92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>ECOGR</t>
         </is>
       </c>
       <c r="B93" s="7" t="n">
-        <v>317.25</v>
+        <v>33.96</v>
       </c>
       <c r="C93" s="8" t="n">
         <v>0.2857</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>29.75</v>
+        <v>-4.52</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>257.5</v>
+        <v>39</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>31.25</v>
+        <v>-4.76</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>324.75</v>
+        <v>44.54</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>-0.232</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>320.25</v>
+        <v>45.72</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>70.06999999999999</v>
+        <v>39.69</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>294.25</v>
+        <v>39.38</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Güçlü sat</t>
         </is>
       </c>
       <c r="N93" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Güçlü sat</t>
         </is>
       </c>
       <c r="O93" s="6" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P93" s="7" t="n">
-        <v>13</v>
+        <v>-1.44</v>
       </c>
       <c r="Q93" s="7" t="n">
-        <v>303</v>
+        <v>34.34</v>
       </c>
       <c r="R93" s="7" t="n">
-        <v>313.75</v>
+        <v>42.68</v>
       </c>
       <c r="S93" s="7" t="n">
-        <v>2.75</v>
+        <v>-10.24</v>
       </c>
       <c r="T93" s="7" t="n">
-        <v>11.5</v>
+        <v>2.56</v>
       </c>
       <c r="U93" s="8" t="n">
-        <v>0.0363</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="V93" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.0834</v>
       </c>
       <c r="W93" s="7" t="n">
-        <v>42.3</v>
+        <v>17.21</v>
       </c>
       <c r="X93" s="7" t="n">
-        <v>62.24</v>
+        <v>42.31</v>
       </c>
       <c r="Y93" s="7" t="n">
-        <v>283</v>
+        <v>41.5</v>
       </c>
       <c r="Z93" s="7" t="n">
-        <v>-8.050000000000001</v>
+        <v>-84.12</v>
       </c>
       <c r="AA93" s="7" t="n">
-        <v>33.97</v>
+        <v>22.31</v>
       </c>
       <c r="AB93" s="6" t="inlineStr"/>
     </row>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="B94" s="5" t="n">
-        <v>133.2</v>
+        <v>133.5</v>
       </c>
       <c r="C94" s="4" t="n">
         <v>0</v>
@@ -9090,22 +9090,22 @@
         <v>161.8</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-15.1</v>
+        <v>-15.2</v>
       </c>
       <c r="G94" s="5" t="n">
         <v>180.7</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>-0.1225</v>
+        <v>-0.1206</v>
       </c>
       <c r="J94" s="5" t="n">
         <v>177.9</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>36.54</v>
+        <v>36.82</v>
       </c>
       <c r="L94" s="5" t="n">
         <v>151.6</v>
@@ -9126,37 +9126,37 @@
         </is>
       </c>
       <c r="P94" s="5" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="Q94" s="5" t="n">
-        <v>133.2</v>
+        <v>133.3</v>
       </c>
       <c r="R94" s="5" t="n">
-        <v>163.9</v>
+        <v>164</v>
       </c>
       <c r="S94" s="5" t="n">
-        <v>-23.4</v>
+        <v>-23.1</v>
       </c>
       <c r="T94" s="5" t="n">
         <v>9.1</v>
       </c>
       <c r="U94" s="4" t="n">
-        <v>0.068</v>
+        <v>0.0678</v>
       </c>
       <c r="V94" s="4" t="n">
-        <v>0.0624</v>
+        <v>0.0623</v>
       </c>
       <c r="W94" s="5" t="n">
         <v>22.78</v>
       </c>
       <c r="X94" s="5" t="n">
-        <v>21.67</v>
+        <v>21.64</v>
       </c>
       <c r="Y94" s="5" t="n">
         <v>140.1</v>
       </c>
       <c r="Z94" s="5" t="n">
-        <v>-79.19</v>
+        <v>-78.47</v>
       </c>
       <c r="AA94" s="5" t="n">
         <v>17.22</v>
@@ -9166,317 +9166,317 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B95" s="7" t="n">
-        <v>97.95</v>
+        <v>317</v>
       </c>
       <c r="C95" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.2857</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>-9.699999999999999</v>
+        <v>29.75</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>110.2</v>
+        <v>257.5</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>-9.449999999999999</v>
+        <v>31.25</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>112.75</v>
+        <v>324.5</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>-0.2</v>
+        <v>0.19</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>-0.08710000000000001</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J95" s="7" t="n">
-        <v>114.9</v>
+        <v>320.25</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>38.03</v>
+        <v>69.98</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>105.45</v>
+        <v>294.25</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Güçlü al</t>
         </is>
       </c>
       <c r="O95" s="6" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="P95" s="7" t="n">
-        <v>-2.7</v>
+        <v>13</v>
       </c>
       <c r="Q95" s="7" t="n">
-        <v>98.2</v>
+        <v>303</v>
       </c>
       <c r="R95" s="7" t="n">
-        <v>113.45</v>
+        <v>313.75</v>
       </c>
       <c r="S95" s="7" t="n">
-        <v>-11.35</v>
+        <v>2.5</v>
       </c>
       <c r="T95" s="7" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="U95" s="8" t="n">
-        <v>0.0482</v>
+        <v>0.0363</v>
       </c>
       <c r="V95" s="8" t="n">
-        <v>0.0424</v>
+        <v>0.038</v>
       </c>
       <c r="W95" s="7" t="n">
-        <v>21.3</v>
+        <v>42.3</v>
       </c>
       <c r="X95" s="7" t="n">
-        <v>40.65</v>
+        <v>62.33</v>
       </c>
       <c r="Y95" s="7" t="n">
-        <v>110.5</v>
+        <v>283</v>
       </c>
       <c r="Z95" s="7" t="n">
-        <v>-97.13</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="AA95" s="7" t="n">
-        <v>16.38</v>
+        <v>33.97</v>
       </c>
       <c r="AB95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RYGYO</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>40.76</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1</v>
+        <v>0.4286</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>6.88</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>32.86</v>
+        <v>110.2</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>6.44</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>42.48</v>
+        <v>112.75</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.23</v>
+        <v>-0.2</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>0.285</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>41.44</v>
+        <v>114.9</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>78.90000000000001</v>
+        <v>37.92</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>36.48</v>
+        <v>105.45</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Nötr</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="P96" s="5" t="n">
-        <v>2.46</v>
+        <v>-2.7</v>
       </c>
       <c r="Q96" s="5" t="n">
-        <v>41.44</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="R96" s="5" t="n">
-        <v>39.36</v>
+        <v>113.45</v>
       </c>
       <c r="S96" s="5" t="n">
-        <v>8.98</v>
+        <v>-11.45</v>
       </c>
       <c r="T96" s="5" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="U96" s="4" t="n">
-        <v>0.0391</v>
+        <v>0.0482</v>
       </c>
       <c r="V96" s="4" t="n">
-        <v>0.0434</v>
+        <v>0.0425</v>
       </c>
       <c r="W96" s="5" t="n">
-        <v>39.53</v>
+        <v>21.3</v>
       </c>
       <c r="X96" s="5" t="n">
-        <v>94.43000000000001</v>
+        <v>40.55</v>
       </c>
       <c r="Y96" s="5" t="n">
-        <v>38.18</v>
+        <v>110.5</v>
       </c>
       <c r="Z96" s="5" t="n">
-        <v>-6.98</v>
+        <v>-97.70999999999999</v>
       </c>
       <c r="AA96" s="5" t="n">
-        <v>34.26</v>
+        <v>16.38</v>
       </c>
       <c r="AB96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>AYES</t>
+          <t>RYGYO</t>
         </is>
       </c>
       <c r="B97" s="7" t="n">
-        <v>28.8</v>
+        <v>40.54</v>
       </c>
       <c r="C97" s="8" t="n">
-        <v>0.07139999999999999</v>
+        <v>1</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-3.88</v>
+        <v>6.88</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>32.58</v>
+        <v>32.86</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>-1.14</v>
+        <v>6.5</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>34.04</v>
+        <v>42.44</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="I97" s="8" t="n">
-        <v>-0.0775</v>
+        <v>0.2781</v>
       </c>
       <c r="J97" s="7" t="n">
-        <v>33</v>
+        <v>41.44</v>
       </c>
       <c r="K97" s="7" t="n">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="L97" s="7" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>Güçlü al</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="P97" s="7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q97" s="7" t="n">
         <v>41.38</v>
       </c>
-      <c r="L97" s="7" t="n">
-        <v>29.38</v>
-      </c>
-      <c r="M97" s="6" t="inlineStr">
-        <is>
-          <t>Güçlü sat</t>
-        </is>
-      </c>
-      <c r="N97" s="6" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="O97" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="P97" s="7" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="Q97" s="7" t="n">
-        <v>26.94</v>
-      </c>
       <c r="R97" s="7" t="n">
-        <v>32.32</v>
+        <v>39.34</v>
       </c>
       <c r="S97" s="7" t="n">
-        <v>-2.22</v>
+        <v>8.76</v>
       </c>
       <c r="T97" s="7" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="U97" s="8" t="n">
-        <v>0.0377</v>
+        <v>0.0393</v>
       </c>
       <c r="V97" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0437</v>
       </c>
       <c r="W97" s="7" t="n">
-        <v>20.14</v>
+        <v>39.53</v>
       </c>
       <c r="X97" s="7" t="n">
-        <v>58.64</v>
+        <v>89.87</v>
       </c>
       <c r="Y97" s="7" t="n">
-        <v>29.84</v>
+        <v>38.18</v>
       </c>
       <c r="Z97" s="7" t="n">
-        <v>-57.81</v>
+        <v>-9.24</v>
       </c>
       <c r="AA97" s="7" t="n">
-        <v>23.54</v>
+        <v>34.26</v>
       </c>
       <c r="AB97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>15.02</v>
+        <v>5.1</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.4286</v>
+        <v>0.2857</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>14.54</v>
+        <v>5.16</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.66</v>
+        <v>0.17</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>15.92</v>
+        <v>5.28</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>0.0013</v>
+        <v>0.018</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>16.32</v>
+        <v>5.34</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>55.32</v>
+        <v>52.64</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>14.71</v>
+        <v>5.03</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
@@ -9494,85 +9494,85 @@
         </is>
       </c>
       <c r="P98" s="5" t="n">
-        <v>0.17</v>
+        <v>-0.03</v>
       </c>
       <c r="Q98" s="5" t="n">
-        <v>14.68</v>
+        <v>5.11</v>
       </c>
       <c r="R98" s="5" t="n">
-        <v>15.97</v>
+        <v>5.39</v>
       </c>
       <c r="S98" s="5" t="n">
-        <v>0.32</v>
+        <v>-0.17</v>
       </c>
       <c r="T98" s="5" t="n">
-        <v>0.66</v>
+        <v>0.18</v>
       </c>
       <c r="U98" s="4" t="n">
-        <v>0.0438</v>
+        <v>0.0359</v>
       </c>
       <c r="V98" s="4" t="n">
-        <v>0.0457</v>
+        <v>0.0371</v>
       </c>
       <c r="W98" s="5" t="n">
-        <v>22.92</v>
+        <v>18.43</v>
       </c>
       <c r="X98" s="5" t="n">
-        <v>64.94</v>
+        <v>61.79</v>
       </c>
       <c r="Y98" s="5" t="n">
-        <v>16.11</v>
+        <v>4.56</v>
       </c>
       <c r="Z98" s="5" t="n">
-        <v>-46.26</v>
+        <v>-30.38</v>
       </c>
       <c r="AA98" s="5" t="n">
-        <v>25.41</v>
+        <v>21.64</v>
       </c>
       <c r="AB98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B99" s="7" t="n">
-        <v>5.09</v>
+        <v>97.3</v>
       </c>
       <c r="C99" s="8" t="n">
-        <v>0.2857</v>
+        <v>0.2143</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.12</v>
+        <v>1.4</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>5.16</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.17</v>
+        <v>-2.4</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>5.28</v>
+        <v>114.55</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>-0.1</v>
+        <v>0.26</v>
       </c>
       <c r="I99" s="8" t="n">
-        <v>0.016</v>
+        <v>-0.0803</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>5.34</v>
+        <v>117.5</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>52.18</v>
+        <v>52.08</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>5.03</v>
+        <v>102.85</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="N99" s="6" t="inlineStr">
@@ -9586,81 +9586,81 @@
         </is>
       </c>
       <c r="P99" s="7" t="n">
-        <v>-0.03</v>
+        <v>1.85</v>
       </c>
       <c r="Q99" s="7" t="n">
-        <v>5.11</v>
+        <v>93.75</v>
       </c>
       <c r="R99" s="7" t="n">
-        <v>5.39</v>
+        <v>107.2</v>
       </c>
       <c r="S99" s="7" t="n">
-        <v>-0.18</v>
+        <v>-7.1</v>
       </c>
       <c r="T99" s="7" t="n">
-        <v>0.18</v>
+        <v>4.95</v>
       </c>
       <c r="U99" s="8" t="n">
-        <v>0.036</v>
+        <v>0.0506</v>
       </c>
       <c r="V99" s="8" t="n">
-        <v>0.0372</v>
+        <v>0.0605</v>
       </c>
       <c r="W99" s="7" t="n">
-        <v>18.43</v>
+        <v>24.64</v>
       </c>
       <c r="X99" s="7" t="n">
-        <v>61.07</v>
+        <v>60</v>
       </c>
       <c r="Y99" s="7" t="n">
-        <v>4.56</v>
+        <v>106.65</v>
       </c>
       <c r="Z99" s="7" t="n">
-        <v>-31.65</v>
+        <v>-74.13</v>
       </c>
       <c r="AA99" s="7" t="n">
-        <v>21.64</v>
+        <v>23.34</v>
       </c>
       <c r="AB99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>DUNYH</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
-        <v>150.3</v>
+        <v>14.98</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0.7857</v>
+        <v>0.4286</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>16.8</v>
+        <v>0.09</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>128.3</v>
+        <v>14.54</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>6.5</v>
+        <v>0.67</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>155.2</v>
+        <v>15.91</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0013</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>159.6</v>
+        <v>16.32</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>60.61</v>
+        <v>54.92</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>146.5</v>
+        <v>14.71</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -9674,136 +9674,136 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Nötr</t>
         </is>
       </c>
       <c r="P100" s="5" t="n">
-        <v>6.2</v>
+        <v>0.17</v>
       </c>
       <c r="Q100" s="5" t="n">
-        <v>155.3</v>
+        <v>14.67</v>
       </c>
       <c r="R100" s="5" t="n">
-        <v>160.4</v>
+        <v>15.96</v>
       </c>
       <c r="S100" s="5" t="n">
-        <v>5.8</v>
+        <v>0.28</v>
       </c>
       <c r="T100" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="U100" s="4" t="n">
-        <v>0.0553</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="V100" s="4" t="n">
-        <v>0.05139999999999999</v>
+        <v>0.0458</v>
       </c>
       <c r="W100" s="5" t="n">
-        <v>29.43</v>
+        <v>22.92</v>
       </c>
       <c r="X100" s="5" t="n">
-        <v>67.34</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="Y100" s="5" t="n">
-        <v>134.5</v>
+        <v>16.11</v>
       </c>
       <c r="Z100" s="5" t="n">
-        <v>-32.18</v>
+        <v>-47.69</v>
       </c>
       <c r="AA100" s="5" t="n">
-        <v>23.37</v>
+        <v>25.41</v>
       </c>
       <c r="AB100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>GSDDE</t>
+          <t>METRO</t>
         </is>
       </c>
       <c r="B101" s="7" t="n">
-        <v>13.54</v>
+        <v>7.32</v>
       </c>
       <c r="C101" s="8" t="n">
         <v>0.07139999999999999</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.45</v>
+        <v>-1.12</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>13.16</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>1.12</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>14.57</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>0.008199999999999999</v>
+        <v>-0.1644</v>
       </c>
       <c r="J101" s="7" t="n">
-        <v>15.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>53.2</v>
+        <v>32.47</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>13.4</v>
+        <v>8.31</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>Güçlü al</t>
+          <t>Güçlü sat</t>
         </is>
       </c>
       <c r="N101" s="6" t="inlineStr">
         <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
           <t>Al</t>
         </is>
       </c>
-      <c r="O101" s="6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
       <c r="P101" s="7" t="n">
-        <v>-0.08</v>
+        <v>-0.35</v>
       </c>
       <c r="Q101" s="7" t="n">
-        <v>13.36</v>
+        <v>7.09</v>
       </c>
       <c r="R101" s="7" t="n">
-        <v>14.87</v>
+        <v>8.75</v>
       </c>
       <c r="S101" s="7" t="n">
-        <v>-0.7</v>
+        <v>-1.45</v>
       </c>
       <c r="T101" s="7" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="U101" s="8" t="n">
-        <v>0.0649</v>
+        <v>0.0549</v>
       </c>
       <c r="V101" s="8" t="n">
-        <v>0.0585</v>
+        <v>0.0522</v>
       </c>
       <c r="W101" s="7" t="n">
-        <v>23.04</v>
+        <v>27.85</v>
       </c>
       <c r="X101" s="7" t="n">
-        <v>57.04</v>
+        <v>26.2</v>
       </c>
       <c r="Y101" s="7" t="n">
-        <v>14.39</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Z101" s="7" t="n">
-        <v>-53.76</v>
+        <v>-91.70999999999999</v>
       </c>
       <c r="AA101" s="7" t="n">
-        <v>30.37</v>
+        <v>11.27</v>
       </c>
       <c r="AB101" s="6" t="inlineStr"/>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>06.08.2026 10:04</t>
+          <t>06.08.2026 10:35</t>
         </is>
       </c>
     </row>
